--- a/SimulationResult/저널 시뮬레이션.xlsx
+++ b/SimulationResult/저널 시뮬레이션.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjrnj\PycharmProjects\Satellite-Simulation\SimulationResult\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태성\PycharmProjects\Satellite-Simulation\SimulationResult\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139FB024-7589-4FE4-AE4C-D69B55312493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1499332-5C25-478A-A1E3-39FA9896DBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24690" yWindow="3315" windowWidth="21600" windowHeight="11385" tabRatio="1000" xr2:uid="{E6726085-0747-4589-856F-AE988516A596}"/>
+    <workbookView xWindow="-27885" yWindow="2490" windowWidth="25755" windowHeight="12885" tabRatio="1000" activeTab="4" xr2:uid="{E6726085-0747-4589-856F-AE988516A596}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="86" r:id="rId1"/>
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -967,7 +967,7 @@
                 <a:pPr>
                   <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -977,7 +977,7 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Average</a:t>
@@ -985,14 +985,14 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> hop counts</a:t>
                 </a:r>
                 <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                 </a:endParaRPr>
               </a:p>
@@ -1021,7 +1021,7 @@
               <a:pPr>
                 <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -1050,7 +1050,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -1105,10 +1105,7 @@
           <a:pPr>
             <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1708,7 +1705,7 @@
                 <a:pPr>
                   <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1718,7 +1715,7 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Maximum tolerant</a:t>
@@ -1726,14 +1723,14 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> angular velocity (mrad/s)</a:t>
                 </a:r>
                 <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                 </a:endParaRPr>
               </a:p>
@@ -1762,7 +1759,7 @@
               <a:pPr>
                 <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -1841,7 +1838,7 @@
                 <a:pPr>
                   <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1851,14 +1848,14 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Sum of transmission failures (thousands)</a:t>
                 </a:r>
                 <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                 </a:endParaRPr>
               </a:p>
@@ -1887,7 +1884,7 @@
               <a:pPr>
                 <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -1974,10 +1971,7 @@
           <a:pPr>
             <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -2577,7 +2571,7 @@
                 <a:pPr>
                   <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -2587,7 +2581,7 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Maximum tolerant</a:t>
@@ -2595,14 +2589,14 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> angular velocity (mrad/s)</a:t>
                 </a:r>
                 <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                 </a:endParaRPr>
               </a:p>
@@ -2631,7 +2625,7 @@
               <a:pPr>
                 <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -2712,7 +2706,7 @@
                 <a:pPr>
                   <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -2722,14 +2716,14 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Sum of overhead signaling messages (X10,000)</a:t>
                 </a:r>
                 <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                 </a:endParaRPr>
               </a:p>
@@ -2758,7 +2752,7 @@
               <a:pPr>
                 <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -2789,7 +2783,7 @@
             <a:pPr>
               <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2845,10 +2839,7 @@
           <a:pPr>
             <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -3510,7 +3501,7 @@
                 <a:pPr>
                   <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3520,7 +3511,7 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Maximum tolerant</a:t>
@@ -3528,14 +3519,14 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> angular velocity (mrad/s)</a:t>
                 </a:r>
                 <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                 </a:endParaRPr>
               </a:p>
@@ -3564,7 +3555,7 @@
               <a:pPr>
                 <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3596,7 +3587,7 @@
             <a:pPr>
               <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3645,7 +3636,7 @@
                 <a:pPr>
                   <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3655,7 +3646,7 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>End</a:t>
@@ -3663,14 +3654,14 @@
                 <a:r>
                   <a:rPr lang="en-US" altLang="ko-KR" sz="1800" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> to end propagation delay (ms)</a:t>
                 </a:r>
                 <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                 </a:endParaRPr>
               </a:p>
@@ -3699,7 +3690,7 @@
               <a:pPr>
                 <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3783,10 +3774,7 @@
           <a:pPr>
             <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>

--- a/SimulationResult/저널 시뮬레이션.xlsx
+++ b/SimulationResult/저널 시뮬레이션.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태성\PycharmProjects\Satellite-Simulation\SimulationResult\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1499332-5C25-478A-A1E3-39FA9896DBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A80356-7658-4F9C-A516-2E6EB4CCAC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27885" yWindow="2490" windowWidth="25755" windowHeight="12885" tabRatio="1000" activeTab="4" xr2:uid="{E6726085-0747-4589-856F-AE988516A596}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="1000" activeTab="4" xr2:uid="{E6726085-0747-4589-856F-AE988516A596}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="86" r:id="rId1"/>
@@ -255,11 +255,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -693,37 +690,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>34.559870064967498</c:v>
+                  <c:v>30.3626116866056</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>33.417521239380299</c:v>
+                  <c:v>29.599442975074101</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>33.824507746126898</c:v>
+                  <c:v>28.9590108129755</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>32.980819590204803</c:v>
+                  <c:v>28.414556329012601</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>32.485607196401801</c:v>
+                  <c:v>27.927128217945501</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>32.154682658670602</c:v>
+                  <c:v>27.354124808828299</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31.8291554222888</c:v>
+                  <c:v>26.9258470764617</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>31.471734132933499</c:v>
+                  <c:v>26.481104258913099</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>31.176531734132901</c:v>
+                  <c:v>26.020649675162399</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>30.857771114442698</c:v>
+                  <c:v>25.572533733133401</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>30.580729635182401</c:v>
+                  <c:v>25.099790104947498</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -765,37 +762,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>31.0516042</c:v>
+                  <c:v>30.437239249037201</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.68111944</c:v>
+                  <c:v>29.647644718779102</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30.602558720000001</c:v>
+                  <c:v>28.989098444351001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>30.314542729999999</c:v>
+                  <c:v>28.490885091149</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30.010324839999999</c:v>
+                  <c:v>27.837273936037199</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>29.834272859999999</c:v>
+                  <c:v>27.388479069209499</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>29.928785609999998</c:v>
+                  <c:v>26.940748440748401</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>29.68685657</c:v>
+                  <c:v>26.498625673420001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>29.48013993</c:v>
+                  <c:v>25.987686156921502</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>29.492663669999999</c:v>
+                  <c:v>25.563308345827</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>29.264407800000001</c:v>
+                  <c:v>25.0803698150924</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -832,7 +829,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
@@ -842,7 +839,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
@@ -850,14 +847,14 @@
                   <a:t>Maximum tolerant</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800" baseline="0">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> angular velocity (mrad/s)</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
@@ -869,8 +866,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.3049139143885396"/>
-              <c:y val="0.92510320632031562"/>
+              <c:x val="0.32047761437908495"/>
+              <c:y val="0.93392263888888893"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -886,7 +883,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
@@ -965,7 +962,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -975,7 +972,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -983,14 +980,14 @@
                   <a:t>Average</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800" baseline="0">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> hop counts</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -1019,7 +1016,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -1082,8 +1079,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.19603599401999727"/>
-          <c:y val="2.4567280848687884E-2"/>
+          <c:x val="0.19291516530106903"/>
+          <c:y val="1.0018061953660983E-2"/>
           <c:w val="0.60792790832044319"/>
           <c:h val="5.6593202231630592E-2"/>
         </c:manualLayout>
@@ -1564,37 +1561,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>74411</c:v>
+                  <c:v>178242</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63012</c:v>
+                  <c:v>169693</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>68422</c:v>
+                  <c:v>160908</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>57465</c:v>
+                  <c:v>156123</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>52791</c:v>
+                  <c:v>142825</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>47620</c:v>
+                  <c:v>130836</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>42255</c:v>
+                  <c:v>114714</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>37736</c:v>
+                  <c:v>100014</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>31911</c:v>
+                  <c:v>82235</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25118</c:v>
+                  <c:v>63184</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>16256</c:v>
+                  <c:v>37581</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1636,37 +1633,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>67378</c:v>
+                  <c:v>176821</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73637</c:v>
+                  <c:v>167422</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>61954</c:v>
+                  <c:v>162767</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>56921</c:v>
+                  <c:v>157639</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>52052</c:v>
+                  <c:v>143118</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>47053</c:v>
+                  <c:v>130938</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>42009</c:v>
+                  <c:v>114493</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>37320</c:v>
+                  <c:v>100041</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>31700</c:v>
+                  <c:v>82323</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25033</c:v>
+                  <c:v>63169</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>16312</c:v>
+                  <c:v>37600</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1703,7 +1700,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -1713,7 +1710,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -1721,14 +1718,14 @@
                   <a:t>Maximum tolerant</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800" baseline="0">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> angular velocity (mrad/s)</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -1740,8 +1737,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.3049139143885396"/>
-              <c:y val="0.92510320632031562"/>
+              <c:x val="0.32896274371278184"/>
+              <c:y val="0.93416235109494272"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1757,7 +1754,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -1836,7 +1833,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -1846,14 +1843,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Sum of transmission failures (thousands)</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -1882,7 +1879,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -1948,8 +1945,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.19603599401999727"/>
-          <c:y val="2.4567280848687884E-2"/>
+          <c:x val="0.19603599868303526"/>
+          <c:y val="1.0072615735787147E-2"/>
           <c:w val="0.60792790832044319"/>
           <c:h val="5.6593202231630592E-2"/>
         </c:manualLayout>
@@ -2037,7 +2034,17 @@
   <c:chart>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10799771241830065"/>
+          <c:y val="0.10166930667248666"/>
+          <c:w val="0.87753194444444449"/>
+          <c:h val="0.77337388888888892"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -2430,37 +2437,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>353601072</c:v>
+                  <c:v>847005984</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>299433024</c:v>
+                  <c:v>806381136</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>325141344</c:v>
+                  <c:v>764634816</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>273073680</c:v>
+                  <c:v>741896496</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>250862832</c:v>
+                  <c:v>678704400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>226290240</c:v>
+                  <c:v>621732672</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>200795760</c:v>
+                  <c:v>545120928</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>179321472</c:v>
+                  <c:v>475266528</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>151641072</c:v>
+                  <c:v>390780720</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>119360736</c:v>
+                  <c:v>300250368</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>77248512</c:v>
+                  <c:v>178584912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2502,37 +2509,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>320180256</c:v>
+                  <c:v>840253392</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>349923024</c:v>
+                  <c:v>795589344</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>294405408</c:v>
+                  <c:v>773468784</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>270488592</c:v>
+                  <c:v>749100528</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>247351104</c:v>
+                  <c:v>680096736</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>223595856</c:v>
+                  <c:v>622217376</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>199626768</c:v>
+                  <c:v>544070736</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>177344640</c:v>
+                  <c:v>475394832</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>150638400</c:v>
+                  <c:v>391198896</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>118956816</c:v>
+                  <c:v>300179088</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>77514624</c:v>
+                  <c:v>178675200</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2569,7 +2576,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -2579,7 +2586,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -2587,14 +2594,14 @@
                   <a:t>Maximum tolerant</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800" baseline="0">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> angular velocity (mrad/s)</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -2606,8 +2613,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.3049139143885396"/>
-              <c:y val="0.92510320632031562"/>
+              <c:x val="0.32485008169934643"/>
+              <c:y val="0.93568652777777761"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -2623,7 +2630,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -2704,7 +2711,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -2714,14 +2721,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>Sum of overhead signaling messages (X10,000)</a:t>
+                  <a:t>overhead signaling messages (X10,000)</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -2733,8 +2740,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="6.581102627392324E-3"/>
-              <c:y val="0.12223461191820542"/>
+              <c:x val="5.1879084967320259E-3"/>
+              <c:y val="0.19102625000000001"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -2750,7 +2757,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -2816,8 +2823,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.19603599401999727"/>
-          <c:y val="2.4567280848687884E-2"/>
+          <c:x val="0.19603604014196879"/>
+          <c:y val="2.0157108560754946E-2"/>
           <c:w val="0.60792790832044319"/>
           <c:h val="5.6593202231630592E-2"/>
         </c:manualLayout>
@@ -3345,37 +3352,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>159.201953969085</c:v>
+                  <c:v>131.31698690150799</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150.60490596428099</c:v>
+                  <c:v>125.65178925574099</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>154.03232667006</c:v>
+                  <c:v>121.071620669734</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>147.58080733018801</c:v>
+                  <c:v>117.224850329554</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>144.15814895314301</c:v>
+                  <c:v>113.32760805916899</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>141.64013690680301</c:v>
+                  <c:v>109.50034954281701</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>139.18398865168899</c:v>
+                  <c:v>106.025345091734</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>136.58363798812101</c:v>
+                  <c:v>102.79975564385499</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>134.351798294237</c:v>
+                  <c:v>99.250006089705096</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>132.003378712461</c:v>
+                  <c:v>95.873429446079797</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>129.97786432212999</c:v>
+                  <c:v>92.088473209434994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3411,14 +3418,14 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="8"/>
+            <c:symbol val="star"/>
+            <c:size val="15"/>
             <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:noFill/>
+              <a:noFill/>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -3430,37 +3437,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>145.21451870000001</c:v>
+                  <c:v>131.53318820304901</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150.16992210000001</c:v>
+                  <c:v>125.819328392579</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>141.7050811</c:v>
+                  <c:v>121.192992300516</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>138.9176827</c:v>
+                  <c:v>117.51520846343401</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>136.30179050000001</c:v>
+                  <c:v>113.030476533304</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>134.3821691</c:v>
+                  <c:v>109.59675563099</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>133.26504170000001</c:v>
+                  <c:v>106.046529629383</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>131.15370129999999</c:v>
+                  <c:v>102.792956326295</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>129.120767</c:v>
+                  <c:v>99.199026695299196</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>128.026116</c:v>
+                  <c:v>95.865488785296293</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>126.1071443</c:v>
+                  <c:v>91.908538983389207</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3499,7 +3506,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -3509,7 +3516,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -3517,14 +3524,14 @@
                   <a:t>Maximum tolerant</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800" baseline="0">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> angular velocity (mrad/s)</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -3536,8 +3543,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.3049139143885396"/>
-              <c:y val="0.92510320632031562"/>
+              <c:x val="0.33189101307189539"/>
+              <c:y val="0.9427420833333332"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -3553,7 +3560,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -3634,7 +3641,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -3644,7 +3651,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -3652,14 +3659,14 @@
                   <a:t>End</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="1800" baseline="0">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> to end propagation delay (ms)</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -3671,8 +3678,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="6.581102627392324E-3"/>
-              <c:y val="0.15359988879262909"/>
+              <c:x val="3.4683823529411757E-3"/>
+              <c:y val="0.24179430555555556"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -3688,7 +3695,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -3751,9 +3758,9 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.19603599401999727"/>
-          <c:y val="2.4567280848687884E-2"/>
-          <c:w val="0.73702092722906187"/>
+          <c:x val="0.19492998285604765"/>
+          <c:y val="1.3254242516344215E-2"/>
+          <c:w val="0.60689827170777855"/>
           <c:h val="5.6770269104549569E-2"/>
         </c:manualLayout>
       </c:layout>
@@ -6001,15 +6008,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>419099</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>133349</xdr:rowOff>
+      <xdr:colOff>432706</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>106132</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>466724</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>161924</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>426277</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>162382</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6021,7 +6028,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
+          <a:graphicFrameLocks noChangeAspect="1"/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -6043,16 +6050,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676274</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>598761</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>10839</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>181349</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>46724</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6064,7 +6071,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
+          <a:graphicFrameLocks noChangeAspect="1"/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -6087,15 +6094,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
+      <xdr:colOff>485774</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>570186</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>182289</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>421715</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>132449</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6129,16 +6136,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>507465</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>48984</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>513036</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>191814</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>501037</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>105234</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6485,7 +6492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B057519C-BCF1-431B-8A6B-7DEB49978D6C}">
-  <dimension ref="A1:Y41"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -7756,484 +7763,741 @@
       <c r="A31">
         <v>1E-3</v>
       </c>
-      <c r="B31" s="1">
-        <v>34.559870064967498</v>
-      </c>
-      <c r="C31" s="1">
-        <v>159.201953969085</v>
+      <c r="B31">
+        <v>30.3626116866056</v>
+      </c>
+      <c r="C31">
+        <v>131.31698690150799</v>
       </c>
       <c r="D31">
-        <v>74411</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0.743738130934532</v>
+        <v>178242</v>
+      </c>
+      <c r="E31">
+        <v>1.78740686515377</v>
       </c>
       <c r="F31">
-        <v>353601072</v>
-      </c>
-      <c r="G31" s="1">
-        <v>3534.2435982008901</v>
+        <f>D31*3*1584</f>
+        <v>847005984</v>
+      </c>
+      <c r="G31">
+        <f>F31/A31</f>
+        <v>847005984000</v>
       </c>
       <c r="I31">
-        <v>1.0250000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="J31">
-        <v>31.0516042</v>
+        <v>30.437239249037201</v>
       </c>
       <c r="K31">
-        <v>145.21451870000001</v>
+        <v>131.53318820304901</v>
       </c>
       <c r="L31">
-        <v>67378</v>
+        <v>176821</v>
       </c>
       <c r="M31">
-        <v>0.67344327800000003</v>
+        <v>1.77331715340179</v>
       </c>
       <c r="N31">
-        <v>320180256</v>
+        <v>840253392</v>
       </c>
       <c r="O31">
-        <v>3200.2024590000001</v>
+        <v>8426.8031129653391</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
+        <v>1.0250000000000001E-3</v>
+      </c>
+      <c r="B32">
+        <v>29.599442975074101</v>
+      </c>
+      <c r="C32">
+        <v>125.65178925574099</v>
+      </c>
+      <c r="D32">
+        <v>169693</v>
+      </c>
+      <c r="E32">
+        <v>1.70005810691672</v>
+      </c>
+      <c r="F32">
+        <f>D32*3*1584</f>
+        <v>806381136</v>
+      </c>
+      <c r="G32">
+        <f>F32/A32</f>
+        <v>786713303414.63403</v>
+      </c>
+      <c r="I32">
+        <v>1.0250000000000001E-3</v>
+      </c>
+      <c r="J32">
+        <v>29.647644718779102</v>
+      </c>
+      <c r="K32">
+        <v>125.819328392579</v>
+      </c>
+      <c r="L32">
+        <v>167422</v>
+      </c>
+      <c r="M32">
+        <v>1.6776255799272499</v>
+      </c>
+      <c r="N32">
+        <v>795589344</v>
+      </c>
+      <c r="O32">
+        <v>7972.0767558142998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>1.0499999999999999E-3</v>
       </c>
-      <c r="B32" s="1">
-        <v>33.417521239380299</v>
-      </c>
-      <c r="C32" s="1">
-        <v>150.60490596428099</v>
-      </c>
-      <c r="D32">
-        <v>63012</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0.629805097451274</v>
-      </c>
-      <c r="F32">
-        <v>299433024</v>
-      </c>
-      <c r="G32" s="1">
-        <v>2992.8338230884501</v>
-      </c>
-      <c r="I32">
-        <v>1E-3</v>
-      </c>
-      <c r="J32">
-        <v>31.68111944</v>
-      </c>
-      <c r="K32">
-        <v>150.16992210000001</v>
-      </c>
-      <c r="L32">
-        <v>73637</v>
-      </c>
-      <c r="M32">
-        <v>0.73600199899999996</v>
-      </c>
-      <c r="N32">
-        <v>349923024</v>
-      </c>
-      <c r="O32">
-        <v>3497.481499</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>1.0250000000000001E-3</v>
-      </c>
-      <c r="B33" s="1">
-        <v>33.824507746126898</v>
-      </c>
-      <c r="C33" s="1">
-        <v>154.03232667006</v>
+      <c r="B33">
+        <v>28.9590108129755</v>
+      </c>
+      <c r="C33">
+        <v>121.071620669734</v>
       </c>
       <c r="D33">
-        <v>68422</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0.68387806096951498</v>
+        <v>160908</v>
+      </c>
+      <c r="E33">
+        <v>1.61101321585903</v>
       </c>
       <c r="F33">
-        <v>325141344</v>
-      </c>
-      <c r="G33" s="1">
-        <v>3249.78854572713</v>
+        <f>D33*3*1584</f>
+        <v>764634816</v>
+      </c>
+      <c r="G33">
+        <f>F33/A33</f>
+        <v>728223634285.71436</v>
       </c>
       <c r="I33">
         <v>1.0499999999999999E-3</v>
       </c>
       <c r="J33">
-        <v>30.602558720000001</v>
+        <v>28.989098444351001</v>
       </c>
       <c r="K33">
-        <v>141.7050811</v>
+        <v>121.192992300516</v>
       </c>
       <c r="L33">
-        <v>61954</v>
+        <v>162767</v>
       </c>
       <c r="M33">
-        <v>0.61923038500000005</v>
+        <v>1.6293971609906499</v>
       </c>
       <c r="N33">
-        <v>294405408</v>
+        <v>773468784</v>
       </c>
       <c r="O33">
-        <v>2942.582789</v>
+        <v>7742.89530902756</v>
+      </c>
+      <c r="Q33">
+        <v>1.075E-3</v>
+      </c>
+      <c r="R33">
+        <v>28.490885091149</v>
+      </c>
+      <c r="S33">
+        <v>117.51520846343401</v>
+      </c>
+      <c r="T33">
+        <v>157639</v>
+      </c>
+      <c r="U33">
+        <v>1.5763742362576301</v>
+      </c>
+      <c r="V33">
+        <v>749100528</v>
+      </c>
+      <c r="W33">
+        <v>7490.9303706962901</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1.075E-3</v>
       </c>
-      <c r="B34" s="1">
-        <v>32.980819590204803</v>
-      </c>
-      <c r="C34" s="1">
-        <v>147.58080733018801</v>
+      <c r="B34">
+        <v>28.414556329012601</v>
+      </c>
+      <c r="C34">
+        <v>117.224850329554</v>
       </c>
       <c r="D34">
-        <v>57465</v>
-      </c>
-      <c r="E34" s="1">
-        <v>0.57436281859070404</v>
+        <v>156123</v>
+      </c>
+      <c r="E34">
+        <v>1.56147983677388</v>
       </c>
       <c r="F34">
-        <v>273073680</v>
-      </c>
-      <c r="G34" s="1">
-        <v>2729.3721139430199</v>
+        <f>D34*3*1584</f>
+        <v>741896496</v>
+      </c>
+      <c r="G34">
+        <f>F34/A34</f>
+        <v>690136275348.83716</v>
       </c>
       <c r="I34">
         <v>1.075E-3</v>
       </c>
       <c r="J34">
-        <v>30.314542729999999</v>
+        <v>28.490885091149</v>
       </c>
       <c r="K34">
-        <v>138.9176827</v>
+        <v>117.51520846343401</v>
       </c>
       <c r="L34">
-        <v>56921</v>
+        <v>157639</v>
       </c>
       <c r="M34">
-        <v>0.56892553700000004</v>
+        <v>1.5763742362576301</v>
       </c>
       <c r="N34">
-        <v>270488592</v>
+        <v>749100528</v>
       </c>
       <c r="O34">
-        <v>2703.5341530000001</v>
+        <v>7490.9303706962901</v>
+      </c>
+      <c r="Q34">
+        <v>1.0499999999999999E-3</v>
+      </c>
+      <c r="R34">
+        <v>28.989098444351001</v>
+      </c>
+      <c r="S34">
+        <v>121.192992300516</v>
+      </c>
+      <c r="T34">
+        <v>162767</v>
+      </c>
+      <c r="U34">
+        <v>1.6293971609906499</v>
+      </c>
+      <c r="V34">
+        <v>773468784</v>
+      </c>
+      <c r="W34">
+        <v>7742.89530902756</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="B35">
-        <v>32.485607196401801</v>
+        <v>27.927128217945501</v>
       </c>
       <c r="C35">
-        <v>144.15814895314301</v>
+        <v>113.32760805916899</v>
       </c>
       <c r="D35">
-        <v>52791</v>
-      </c>
-      <c r="E35" s="1">
-        <v>0.52764617691154403</v>
+        <v>142825</v>
+      </c>
+      <c r="E35">
+        <v>1.4278930267433101</v>
       </c>
       <c r="F35">
-        <v>250862832</v>
-      </c>
-      <c r="G35" s="1">
-        <v>2507.3746326836499</v>
+        <f t="shared" ref="F35:F41" si="1">D35*3*1584</f>
+        <v>678704400</v>
+      </c>
+      <c r="G35">
+        <f t="shared" ref="G35" si="2">F35/A35</f>
+        <v>617004000000</v>
       </c>
       <c r="I35">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="J35">
-        <v>30.010324839999999</v>
+        <v>27.837273936037199</v>
       </c>
       <c r="K35">
-        <v>136.30179050000001</v>
+        <v>113.030476533304</v>
       </c>
       <c r="L35">
-        <v>52052</v>
+        <v>143118</v>
       </c>
       <c r="M35">
-        <v>0.52025986999999996</v>
+        <v>1.43079368570485</v>
       </c>
       <c r="N35">
-        <v>247351104</v>
+        <v>680096736</v>
       </c>
       <c r="O35">
-        <v>2472.274903</v>
+        <v>6799.1315944694898</v>
+      </c>
+      <c r="Q35">
+        <v>1.0250000000000001E-3</v>
+      </c>
+      <c r="R35">
+        <v>29.647644718779102</v>
+      </c>
+      <c r="S35">
+        <v>125.819328392579</v>
+      </c>
+      <c r="T35">
+        <v>167422</v>
+      </c>
+      <c r="U35">
+        <v>1.6776255799272499</v>
+      </c>
+      <c r="V35">
+        <v>795589344</v>
+      </c>
+      <c r="W35">
+        <v>7972.0767558142998</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1.1249999999999999E-3</v>
       </c>
-      <c r="B36" s="1">
-        <v>32.154682658670602</v>
-      </c>
-      <c r="C36" s="1">
-        <v>141.64013690680301</v>
+      <c r="B36">
+        <v>27.354124808828299</v>
+      </c>
+      <c r="C36">
+        <v>109.50034954281701</v>
       </c>
       <c r="D36">
-        <v>47620</v>
-      </c>
-      <c r="E36" s="1">
-        <v>0.475962018990504</v>
+        <v>130836</v>
+      </c>
+      <c r="E36">
+        <v>1.3078237922451701</v>
       </c>
       <c r="F36">
-        <v>226290240</v>
-      </c>
-      <c r="G36" s="1">
-        <v>2261.7715142428701</v>
+        <f>D36*3*1584</f>
+        <v>621732672</v>
+      </c>
+      <c r="G36">
+        <f>F36/A36</f>
+        <v>552651264000</v>
       </c>
       <c r="I36">
         <v>1.1249999999999999E-3</v>
       </c>
       <c r="J36">
-        <v>29.834272859999999</v>
+        <v>27.388479069209499</v>
       </c>
       <c r="K36">
-        <v>134.3821691</v>
+        <v>109.59675563099</v>
       </c>
       <c r="L36">
-        <v>47053</v>
+        <v>130938</v>
       </c>
       <c r="M36">
-        <v>0.47029485300000001</v>
+        <v>1.3088041261844701</v>
       </c>
       <c r="N36">
-        <v>223595856</v>
+        <v>622217376</v>
       </c>
       <c r="O36">
-        <v>2234.8411390000001</v>
+        <v>6219.43720762864</v>
+      </c>
+      <c r="Q36">
+        <v>1E-3</v>
+      </c>
+      <c r="R36">
+        <v>30.437239249037201</v>
+      </c>
+      <c r="S36">
+        <v>131.53318820304901</v>
+      </c>
+      <c r="T36">
+        <v>176821</v>
+      </c>
+      <c r="U36">
+        <v>1.77331715340179</v>
+      </c>
+      <c r="V36">
+        <v>840253392</v>
+      </c>
+      <c r="W36">
+        <v>8426.8031129653391</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1.15E-3</v>
       </c>
-      <c r="B37" s="1">
-        <v>31.8291554222888</v>
-      </c>
-      <c r="C37" s="1">
-        <v>139.18398865168899</v>
+      <c r="B37">
+        <v>26.9258470764617</v>
+      </c>
+      <c r="C37">
+        <v>106.025345091734</v>
       </c>
       <c r="D37">
-        <v>42255</v>
-      </c>
-      <c r="E37" s="1">
-        <v>0.422338830584707</v>
+        <v>114714</v>
+      </c>
+      <c r="E37">
+        <v>1.14656671664167</v>
       </c>
       <c r="F37">
-        <v>200795760</v>
-      </c>
-      <c r="G37" s="1">
-        <v>2006.95412293853</v>
+        <f t="shared" ref="F37:F41" si="3">D37*3*1584</f>
+        <v>545120928</v>
+      </c>
+      <c r="G37">
+        <f t="shared" ref="G37:G38" si="4">F37/A37</f>
+        <v>474018198260.86957</v>
       </c>
       <c r="I37">
         <v>1.15E-3</v>
       </c>
       <c r="J37">
-        <v>29.928785609999998</v>
+        <v>26.940748440748401</v>
       </c>
       <c r="K37">
-        <v>133.26504170000001</v>
+        <v>106.046529629383</v>
       </c>
       <c r="L37">
-        <v>42009</v>
+        <v>114493</v>
       </c>
       <c r="M37">
-        <v>0.41988006</v>
+        <v>1.1443806972653101</v>
       </c>
       <c r="N37">
-        <v>199626768</v>
+        <v>544070736</v>
       </c>
       <c r="O37">
-        <v>1995.270045</v>
+        <v>5438.0970734047596</v>
+      </c>
+      <c r="Q37">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="R37">
+        <v>27.837273936037199</v>
+      </c>
+      <c r="S37">
+        <v>113.030476533304</v>
+      </c>
+      <c r="T37">
+        <v>143118</v>
+      </c>
+      <c r="U37">
+        <v>1.43079368570485</v>
+      </c>
+      <c r="V37">
+        <v>680096736</v>
+      </c>
+      <c r="W37">
+        <v>6799.1315944694898</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1.175E-3</v>
       </c>
-      <c r="B38" s="1">
-        <v>31.471734132933499</v>
-      </c>
-      <c r="C38" s="1">
-        <v>136.58363798812101</v>
+      <c r="B38">
+        <v>26.481104258913099</v>
+      </c>
+      <c r="C38">
+        <v>102.79975564385499</v>
       </c>
       <c r="D38">
-        <v>37736</v>
-      </c>
-      <c r="E38" s="1">
-        <v>0.377171414292853</v>
+        <v>100014</v>
+      </c>
+      <c r="E38">
+        <v>0.99965017141600598</v>
       </c>
       <c r="F38">
-        <v>179321472</v>
-      </c>
-      <c r="G38" s="1">
-        <v>1792.3185607196399</v>
+        <f t="shared" si="3"/>
+        <v>475266528</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="4"/>
+        <v>404482151489.36169</v>
       </c>
       <c r="I38">
         <v>1.175E-3</v>
       </c>
       <c r="J38">
-        <v>29.68685657</v>
+        <v>26.498625673420001</v>
       </c>
       <c r="K38">
-        <v>131.15370129999999</v>
+        <v>102.792956326295</v>
       </c>
       <c r="L38">
-        <v>37320</v>
+        <v>100041</v>
       </c>
       <c r="M38">
-        <v>0.37301349299999997</v>
+        <v>0.99992003918080097</v>
       </c>
       <c r="N38">
-        <v>177344640</v>
+        <v>475394832</v>
       </c>
       <c r="O38">
-        <v>1772.5601200000001</v>
+        <v>4751.62002618716</v>
+      </c>
+      <c r="Q38">
+        <v>1.1249999999999999E-3</v>
+      </c>
+      <c r="R38">
+        <v>27.388479069209499</v>
+      </c>
+      <c r="S38">
+        <v>109.59675563099</v>
+      </c>
+      <c r="T38">
+        <v>130938</v>
+      </c>
+      <c r="U38">
+        <v>1.3088041261844701</v>
+      </c>
+      <c r="V38">
+        <v>622217376</v>
+      </c>
+      <c r="W38">
+        <v>6219.43720762864</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="B39" s="1">
-        <v>31.176531734132901</v>
-      </c>
-      <c r="C39" s="1">
-        <v>134.351798294237</v>
+      <c r="B39">
+        <v>26.020649675162399</v>
+      </c>
+      <c r="C39">
+        <v>99.250006089705096</v>
       </c>
       <c r="D39">
-        <v>31911</v>
-      </c>
-      <c r="E39" s="1">
-        <v>0.31895052473763102</v>
+        <v>82235</v>
+      </c>
+      <c r="E39">
+        <v>0.82193903048475703</v>
       </c>
       <c r="F39">
-        <v>151641072</v>
-      </c>
-      <c r="G39" s="1">
-        <v>1515.6528935532201</v>
+        <f>D39*3*1584</f>
+        <v>390780720</v>
+      </c>
+      <c r="G39">
+        <f>F39/A39</f>
+        <v>325650600000</v>
       </c>
       <c r="I39">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="J39">
-        <v>29.48013993</v>
+        <v>25.987686156921502</v>
       </c>
       <c r="K39">
-        <v>129.120767</v>
+        <v>99.199026695299196</v>
       </c>
       <c r="L39">
-        <v>31700</v>
+        <v>82323</v>
       </c>
       <c r="M39">
-        <v>0.31684157899999998</v>
+        <v>0.82281859070464702</v>
       </c>
       <c r="N39">
-        <v>150638400</v>
+        <v>391198896</v>
       </c>
       <c r="O39">
-        <v>1505.6311840000001</v>
+        <v>3910.0339430284798</v>
+      </c>
+      <c r="Q39">
+        <v>1.15E-3</v>
+      </c>
+      <c r="R39">
+        <v>26.940748440748401</v>
+      </c>
+      <c r="S39">
+        <v>106.046529629383</v>
+      </c>
+      <c r="T39">
+        <v>114493</v>
+      </c>
+      <c r="U39">
+        <v>1.1443806972653101</v>
+      </c>
+      <c r="V39">
+        <v>544070736</v>
+      </c>
+      <c r="W39">
+        <v>5438.0970734047596</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1.225E-3</v>
       </c>
-      <c r="B40" s="1">
-        <v>30.857771114442698</v>
-      </c>
-      <c r="C40" s="1">
-        <v>132.003378712461</v>
+      <c r="B40">
+        <v>25.572533733133401</v>
+      </c>
+      <c r="C40">
+        <v>95.873429446079797</v>
       </c>
       <c r="D40">
-        <v>25118</v>
-      </c>
-      <c r="E40" s="1">
-        <v>0.25105447276361798</v>
+        <v>63184</v>
+      </c>
+      <c r="E40">
+        <v>0.63152423788105905</v>
       </c>
       <c r="F40">
-        <v>119360736</v>
-      </c>
-      <c r="G40" s="1">
-        <v>1193.0108545727101</v>
+        <f>D40*3*1584</f>
+        <v>300250368</v>
+      </c>
+      <c r="G40">
+        <f>F40/A40</f>
+        <v>245102341224.48981</v>
       </c>
       <c r="I40">
         <v>1.225E-3</v>
       </c>
       <c r="J40">
-        <v>29.492663669999999</v>
+        <v>25.563308345827</v>
       </c>
       <c r="K40">
-        <v>128.026116</v>
+        <v>95.865488785296293</v>
       </c>
       <c r="L40">
-        <v>25033</v>
+        <v>63169</v>
       </c>
       <c r="M40">
-        <v>0.25020489800000001</v>
+        <v>0.63137431284357803</v>
       </c>
       <c r="N40">
-        <v>118956816</v>
+        <v>300179088</v>
       </c>
       <c r="O40">
-        <v>1188.973673</v>
+        <v>3000.2907346326801</v>
+      </c>
+      <c r="Q40">
+        <v>1.175E-3</v>
+      </c>
+      <c r="R40">
+        <v>26.498625673420001</v>
+      </c>
+      <c r="S40">
+        <v>102.792956326295</v>
+      </c>
+      <c r="T40">
+        <v>100041</v>
+      </c>
+      <c r="U40">
+        <v>0.99992003918080097</v>
+      </c>
+      <c r="V40">
+        <v>475394832</v>
+      </c>
+      <c r="W40">
+        <v>4751.62002618716</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1.25E-3</v>
       </c>
-      <c r="B41" s="1">
-        <v>30.580729635182401</v>
-      </c>
-      <c r="C41" s="1">
-        <v>129.97786432212999</v>
+      <c r="B41">
+        <v>25.099790104947498</v>
+      </c>
+      <c r="C41">
+        <v>92.088473209434994</v>
       </c>
       <c r="D41">
-        <v>16256</v>
-      </c>
-      <c r="E41" s="1">
-        <v>0.16247876061968999</v>
+        <v>37581</v>
+      </c>
+      <c r="E41">
+        <v>0.37562218890554699</v>
       </c>
       <c r="F41">
-        <v>77248512</v>
-      </c>
-      <c r="G41" s="1">
-        <v>772.09907046476701</v>
+        <f t="shared" ref="F41" si="5">D41*3*1584</f>
+        <v>178584912</v>
+      </c>
+      <c r="G41">
+        <f t="shared" ref="G41" si="6">F41/A41</f>
+        <v>142867929600</v>
       </c>
       <c r="I41">
         <v>1.25E-3</v>
       </c>
       <c r="J41">
-        <v>29.264407800000001</v>
+        <v>25.0803698150924</v>
       </c>
       <c r="K41">
-        <v>126.1071443</v>
+        <v>91.908538983389207</v>
       </c>
       <c r="L41">
-        <v>16312</v>
+        <v>37600</v>
       </c>
       <c r="M41">
-        <v>0.16303848100000001</v>
+        <v>0.37581209395302301</v>
       </c>
       <c r="N41">
-        <v>77514624</v>
+        <v>178675200</v>
       </c>
       <c r="O41">
-        <v>774.75886060000005</v>
+        <v>1785.85907046476</v>
+      </c>
+      <c r="Q41">
+        <v>1.25E-3</v>
+      </c>
+      <c r="R41">
+        <v>25.0803698150924</v>
+      </c>
+      <c r="S41">
+        <v>91.908538983389207</v>
+      </c>
+      <c r="T41">
+        <v>37600</v>
+      </c>
+      <c r="U41">
+        <v>0.37581209395302301</v>
+      </c>
+      <c r="V41">
+        <v>178675200</v>
+      </c>
+      <c r="W41">
+        <v>1785.85907046476</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Q42">
+        <v>1.225E-3</v>
+      </c>
+      <c r="R42">
+        <v>25.563308345827</v>
+      </c>
+      <c r="S42">
+        <v>95.865488785296293</v>
+      </c>
+      <c r="T42">
+        <v>63169</v>
+      </c>
+      <c r="U42">
+        <v>0.63137431284357803</v>
+      </c>
+      <c r="V42">
+        <v>300179088</v>
+      </c>
+      <c r="W42">
+        <v>3000.2907346326801</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Q43">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="R43">
+        <v>25.987686156921502</v>
+      </c>
+      <c r="S43">
+        <v>99.199026695299196</v>
+      </c>
+      <c r="T43">
+        <v>82323</v>
+      </c>
+      <c r="U43">
+        <v>0.82281859070464702</v>
+      </c>
+      <c r="V43">
+        <v>391198896</v>
+      </c>
+      <c r="W43">
+        <v>3910.0339430284798</v>
       </c>
     </row>
   </sheetData>

--- a/SimulationResult/저널 시뮬레이션.xlsx
+++ b/SimulationResult/저널 시뮬레이션.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태성\PycharmProjects\Satellite-Simulation\SimulationResult\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A80356-7658-4F9C-A516-2E6EB4CCAC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA5B604-6513-482C-9A81-88F33921E61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="1000" activeTab="4" xr2:uid="{E6726085-0747-4589-856F-AE988516A596}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="1000" activeTab="4" xr2:uid="{E6726085-0747-4589-856F-AE988516A596}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="86" r:id="rId1"/>
@@ -150,13 +150,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="23">
   <si>
     <t>DTDR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DDR</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -185,10 +181,6 @@
     <t>avg overhead msg</t>
   </si>
   <si>
-    <t>DDRwG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DTDRwG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -201,9 +193,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>24.53865067466267,86.85818723224057</t>
-  </si>
-  <si>
     <t>optimal hop</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -211,12 +200,47 @@
     <t>optimal e2e</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>gain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>overhead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDRS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDRSwG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>avg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>e2e</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vs shortestpath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>,86.85818723224057</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,6 +253,15 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -255,8 +288,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -297,7 +333,17 @@
   <c:chart>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10484681372549019"/>
+          <c:y val="0.10286444444444444"/>
+          <c:w val="0.88373978758169935"/>
+          <c:h val="0.70969305555555573"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -311,7 +357,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DDR</c:v>
+                  <c:v>DDRS</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -382,37 +428,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>40.587996001999002</c:v>
+                  <c:v>37.896801599200401</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38.051264367816003</c:v>
+                  <c:v>34.436701649175397</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>36.727826086956497</c:v>
+                  <c:v>33.088405797101402</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34.976691654172903</c:v>
+                  <c:v>31.4049675162418</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>33.701579210394797</c:v>
+                  <c:v>30.366866566716599</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>32.669155422288803</c:v>
+                  <c:v>29.469855072463702</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31.303688155922</c:v>
+                  <c:v>28.5351124437781</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>30.600439780109902</c:v>
+                  <c:v>28.129435282358799</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>29.281439280359798</c:v>
+                  <c:v>27.2581909045477</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>28.428275862068901</c:v>
+                  <c:v>26.7699050474762</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>27.307146426786598</c:v>
+                  <c:v>26.121439280359802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -432,7 +478,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DDRwG</c:v>
+                  <c:v>DDRSwG</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -454,37 +500,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>25.722418790604699</c:v>
+                  <c:v>25.1891954022988</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25.5968815592203</c:v>
+                  <c:v>25.166896551724101</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.562288855572199</c:v>
+                  <c:v>24.956991504247799</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25.522798600699598</c:v>
+                  <c:v>24.873533233383299</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25.33201399</c:v>
+                  <c:v>24.782328835582199</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25.27149425</c:v>
+                  <c:v>24.7260369815092</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>25.243178409999999</c:v>
+                  <c:v>24.879460269865</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25.07311344</c:v>
+                  <c:v>24.7492253873063</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25.00367816</c:v>
+                  <c:v>24.599170414792599</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25.035572210000002</c:v>
+                  <c:v>24.5712943528235</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>24.819900050000001</c:v>
+                  <c:v>24.4689255372313</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -611,37 +657,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>25.157141429999999</c:v>
+                  <c:v>25.192163918040901</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25.075702150000001</c:v>
+                  <c:v>25.1360219890054</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.144677659999999</c:v>
+                  <c:v>25.073783108445699</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25.11894053</c:v>
+                  <c:v>25.151664167916</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24.962268869999999</c:v>
+                  <c:v>25.081489255372301</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24.92835582</c:v>
+                  <c:v>24.8646176911544</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>24.952043979999999</c:v>
+                  <c:v>24.925097451274301</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>24.807995999999999</c:v>
+                  <c:v>24.786266866566699</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>24.68882559</c:v>
+                  <c:v>24.679520239879999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>24.60172914</c:v>
+                  <c:v>24.599330334832501</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>24.515902050000001</c:v>
+                  <c:v>24.504397801099401</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -762,37 +808,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>30.437239249037201</c:v>
+                  <c:v>30.334299526598699</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29.647644718779102</c:v>
+                  <c:v>29.605405513704099</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28.989098444351001</c:v>
+                  <c:v>28.9913512647774</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28.490885091149</c:v>
+                  <c:v>28.4227518678175</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>27.837273936037199</c:v>
+                  <c:v>27.908460138769399</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>27.388479069209499</c:v>
+                  <c:v>27.4427351965135</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>26.940748440748401</c:v>
+                  <c:v>26.9018361370156</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>26.498625673420001</c:v>
+                  <c:v>26.4699597197373</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25.987686156921502</c:v>
+                  <c:v>26.025747126436698</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25.563308345827</c:v>
+                  <c:v>25.590934532733598</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>25.0803698150924</c:v>
+                  <c:v>25.0942628685657</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -811,7 +857,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="271"/>
+        <c:gapWidth val="115"/>
         <c:axId val="63278767"/>
         <c:axId val="63271567"/>
       </c:barChart>
@@ -822,6 +868,20 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -829,7 +889,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
@@ -839,24 +899,16 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>Maximum tolerant</a:t>
+                  <a:t>Maximum tolerant angular velocity,            (mrad/s)</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> angular velocity (mrad/s)</a:t>
-                </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                 </a:endParaRPr>
               </a:p>
@@ -866,8 +918,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.32047761437908495"/>
-              <c:y val="0.93392263888888893"/>
+              <c:x val="0.26756094771241828"/>
+              <c:y val="0.92404694444444435"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -883,7 +935,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
@@ -915,7 +967,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -962,7 +1014,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -972,7 +1024,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -980,14 +1032,14 @@
                   <a:t>Average</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> hop counts</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3200">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -999,8 +1051,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="6.5811122079631459E-3"/>
-              <c:y val="0.31266656994508851"/>
+              <c:x val="6.5811274509803919E-3"/>
+              <c:y val="0.21388874999999999"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1016,7 +1068,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -1047,9 +1099,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1079,9 +1131,9 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.19291516530106903"/>
+          <c:x val="0.10264558823529411"/>
           <c:y val="1.0018061953660983E-2"/>
-          <c:w val="0.60792790832044319"/>
+          <c:w val="0.88599983660130699"/>
           <c:h val="5.6593202231630592E-2"/>
         </c:manualLayout>
       </c:layout>
@@ -1100,7 +1152,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -1168,7 +1220,17 @@
   <c:chart>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10484681372549019"/>
+          <c:y val="0.10286444444444444"/>
+          <c:w val="0.88373978758169935"/>
+          <c:h val="0.70969305555555573"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1182,7 +1244,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DDR</c:v>
+                  <c:v>DDRS</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1248,49 +1310,49 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>data!$D$3:$D$13</c:f>
+              <c:f>data!$B$3:$B$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>917241</c:v>
+                  <c:v>37.896801599200401</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>717981</c:v>
+                  <c:v>34.436701649175397</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>635083</c:v>
+                  <c:v>33.088405797101402</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>534017</c:v>
+                  <c:v>31.4049675162418</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>465232</c:v>
+                  <c:v>30.366866566716599</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>409712</c:v>
+                  <c:v>29.469855072463702</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>343007</c:v>
+                  <c:v>28.5351124437781</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>304307</c:v>
+                  <c:v>28.129435282358799</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>240404</c:v>
+                  <c:v>27.2581909045477</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>198375</c:v>
+                  <c:v>26.7699050474762</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>140874</c:v>
+                  <c:v>26.121439280359802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-476B-4273-BE60-4157EA253EEB}"/>
+              <c16:uniqueId val="{00000000-81A5-47BC-9ACB-FDA0764BAB01}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1303,7 +1365,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DDRwG</c:v>
+                  <c:v>DDRSwG</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1320,49 +1382,49 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>data!$L$3:$L$13</c:f>
+              <c:f>data!$J$3:$J$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>524948</c:v>
+                  <c:v>25.1891954022988</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>463036</c:v>
+                  <c:v>25.166896551724101</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>421567</c:v>
+                  <c:v>24.956991504247799</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>381768</c:v>
+                  <c:v>24.873533233383299</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>332229</c:v>
+                  <c:v>24.782328835582199</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>291691</c:v>
+                  <c:v>24.7260369815092</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>251203</c:v>
+                  <c:v>24.879460269865</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>217952</c:v>
+                  <c:v>24.7492253873063</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>177395</c:v>
+                  <c:v>24.599170414792599</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>148896</c:v>
+                  <c:v>24.5712943528235</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>106651</c:v>
+                  <c:v>24.4689255372313</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-476B-4273-BE60-4157EA253EEB}"/>
+              <c16:uniqueId val="{00000001-81A5-47BC-9ACB-FDA0764BAB01}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1403,49 +1465,49 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>data!$D$17:$D$27</c:f>
+              <c:f>data!$B$17:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>543522</c:v>
+                  <c:v>41.585260780041096</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>434944</c:v>
+                  <c:v>38.5413193403298</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>356479</c:v>
+                  <c:v>36.256071964017899</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>269013</c:v>
+                  <c:v>33.066126936531703</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>242424</c:v>
+                  <c:v>32.196031980000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>209193</c:v>
+                  <c:v>31.015652169999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>167174</c:v>
+                  <c:v>29.594292849999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>146961</c:v>
+                  <c:v>28.959010490000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>124937</c:v>
+                  <c:v>28.286176909999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>97560</c:v>
+                  <c:v>27.506576710000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>64756</c:v>
+                  <c:v>26.483428289999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-476B-4273-BE60-4157EA253EEB}"/>
+              <c16:uniqueId val="{00000002-81A5-47BC-9ACB-FDA0764BAB01}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1477,49 +1539,49 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>data!$L$17:$L$27</c:f>
+              <c:f>data!$J$17:$J$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>308119</c:v>
+                  <c:v>25.192163918040901</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>269268</c:v>
+                  <c:v>25.1360219890054</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>238810</c:v>
+                  <c:v>25.073783108445699</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>209514</c:v>
+                  <c:v>25.151664167916</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>180895</c:v>
+                  <c:v>25.081489255372301</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>156911</c:v>
+                  <c:v>24.8646176911544</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>133952</c:v>
+                  <c:v>24.925097451274301</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>116756</c:v>
+                  <c:v>24.786266866566699</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>98158</c:v>
+                  <c:v>24.679520239879999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>78548</c:v>
+                  <c:v>24.599330334832501</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>53021</c:v>
+                  <c:v>24.504397801099401</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-476B-4273-BE60-4157EA253EEB}"/>
+              <c16:uniqueId val="{00000003-81A5-47BC-9ACB-FDA0764BAB01}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1556,49 +1618,49 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>data!$D$31:$D$41</c:f>
+              <c:f>data!$B$31:$B$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>178242</c:v>
+                  <c:v>30.3626116866056</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>169693</c:v>
+                  <c:v>29.599442975074101</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>160908</c:v>
+                  <c:v>28.9590108129755</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>156123</c:v>
+                  <c:v>28.414556329012601</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>142825</c:v>
+                  <c:v>27.927128217945501</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>130836</c:v>
+                  <c:v>27.354124808828299</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>114714</c:v>
+                  <c:v>26.9258470764617</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>100014</c:v>
+                  <c:v>26.481104258913099</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>82235</c:v>
+                  <c:v>26.020649675162399</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>63184</c:v>
+                  <c:v>25.572533733133401</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>37581</c:v>
+                  <c:v>25.099790104947498</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-476B-4273-BE60-4157EA253EEB}"/>
+              <c16:uniqueId val="{00000004-81A5-47BC-9ACB-FDA0764BAB01}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1628,49 +1690,49 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>data!$L$31:$L$41</c:f>
+              <c:f>data!$J$31:$J$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>176821</c:v>
+                  <c:v>30.334299526598699</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>167422</c:v>
+                  <c:v>29.605405513704099</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>162767</c:v>
+                  <c:v>28.9913512647774</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>157639</c:v>
+                  <c:v>28.4227518678175</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>143118</c:v>
+                  <c:v>27.908460138769399</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>130938</c:v>
+                  <c:v>27.4427351965135</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>114493</c:v>
+                  <c:v>26.9018361370156</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>100041</c:v>
+                  <c:v>26.4699597197373</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>82323</c:v>
+                  <c:v>26.025747126436698</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>63169</c:v>
+                  <c:v>25.590934532733598</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>37600</c:v>
+                  <c:v>25.0942628685657</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-476B-4273-BE60-4157EA253EEB}"/>
+              <c16:uniqueId val="{00000005-81A5-47BC-9ACB-FDA0764BAB01}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1682,7 +1744,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="271"/>
+        <c:gapWidth val="115"/>
         <c:axId val="63278767"/>
         <c:axId val="63271567"/>
       </c:barChart>
@@ -1693,6 +1755,20 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -1700,9 +1776,9 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1710,22 +1786,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>Maximum tolerant</a:t>
+                  <a:t>Maximum tolerant angular velocity,            (mrad/s)</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> angular velocity (mrad/s)</a:t>
-                </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -1737,8 +1805,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.32896274371278184"/>
-              <c:y val="0.93416235109494272"/>
+              <c:x val="0.205306045751634"/>
+              <c:y val="0.92404694444444435"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1754,9 +1822,9 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
+                    <a:schemeClr val="tx1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -1786,7 +1854,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -1833,7 +1901,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -1843,14 +1911,22 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>Sum of transmission failures (thousands)</a:t>
+                  <a:t>Average</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> hop counts</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3200">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -1862,8 +1938,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="6.581102627392324E-3"/>
-              <c:y val="0.15359988879262909"/>
+              <c:x val="6.5811274509803919E-3"/>
+              <c:y val="0.21388874999999999"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1879,7 +1955,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -1892,7 +1968,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="#,##0_);[Red]\(#,##0\)" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="in"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1910,9 +1986,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1925,9 +2001,6 @@
         <c:crossAx val="63278767"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:dispUnits>
-          <c:builtInUnit val="thousands"/>
-        </c:dispUnits>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1945,9 +2018,9 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.19603599868303526"/>
-          <c:y val="1.0072615735787147E-2"/>
-          <c:w val="0.60792790832044319"/>
+          <c:x val="0.10264558823529411"/>
+          <c:y val="1.0018061953660983E-2"/>
+          <c:w val="0.88599983660130699"/>
           <c:h val="5.6593202231630592E-2"/>
         </c:manualLayout>
       </c:layout>
@@ -1966,7 +2039,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2039,10 +2112,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.10799771241830065"/>
-          <c:y val="0.10166930667248666"/>
-          <c:w val="0.87753194444444449"/>
-          <c:h val="0.77337388888888892"/>
+          <c:x val="0.13709342850563444"/>
+          <c:y val="0.1147191668449961"/>
+          <c:w val="0.85140494764126562"/>
+          <c:h val="0.69274413296240811"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -2058,7 +2131,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DDR</c:v>
+                  <c:v>DDRS</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2124,49 +2197,49 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>data!$F$3:$F$13</c:f>
+              <c:f>data!$D$3:$D$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1170690</c:v>
+                  <c:v>929782</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>930785</c:v>
+                  <c:v>725393</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>810992</c:v>
+                  <c:v>643036</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>678211</c:v>
+                  <c:v>539928</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>580811</c:v>
+                  <c:v>473486</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500536</c:v>
+                  <c:v>414226</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>410915</c:v>
+                  <c:v>348859</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>352760</c:v>
+                  <c:v>309005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>270591</c:v>
+                  <c:v>246242</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>211128</c:v>
+                  <c:v>203959</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>137533</c:v>
+                  <c:v>145987</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5351-4321-B076-84822CFEAA03}"/>
+              <c16:uniqueId val="{00000000-476B-4273-BE60-4157EA253EEB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2179,7 +2252,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DDRwG</c:v>
+                  <c:v>DDRSwG</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2196,49 +2269,49 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>data!$N$3:$N$13</c:f>
+              <c:f>data!$L$3:$L$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>668852</c:v>
+                  <c:v>592755</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>584883</c:v>
+                  <c:v>514729</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>525124</c:v>
+                  <c:v>463209</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>469286</c:v>
+                  <c:v>408459</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>403594</c:v>
+                  <c:v>357995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>351002</c:v>
+                  <c:v>315944</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>298051</c:v>
+                  <c:v>275647</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>254605</c:v>
+                  <c:v>242059</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>201707</c:v>
+                  <c:v>197375</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>160662</c:v>
+                  <c:v>163748</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>105043</c:v>
+                  <c:v>116642</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5351-4321-B076-84822CFEAA03}"/>
+              <c16:uniqueId val="{00000001-476B-4273-BE60-4157EA253EEB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2279,49 +2352,49 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>data!$F$17:$F$27</c:f>
+              <c:f>data!$D$17:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>2174088</c:v>
+                  <c:v>543522</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1739776</c:v>
+                  <c:v>434944</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1425916</c:v>
+                  <c:v>356479</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1076052</c:v>
+                  <c:v>269013</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>969696</c:v>
+                  <c:v>242424</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>836772</c:v>
+                  <c:v>209193</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>668696</c:v>
+                  <c:v>167174</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>587844</c:v>
+                  <c:v>146961</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>499748</c:v>
+                  <c:v>124937</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>390240</c:v>
+                  <c:v>97560</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>259024</c:v>
+                  <c:v>64756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-5351-4321-B076-84822CFEAA03}"/>
+              <c16:uniqueId val="{00000002-476B-4273-BE60-4157EA253EEB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2353,49 +2426,49 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>data!$N$17:$N$27</c:f>
+              <c:f>data!$L$17:$L$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1232476</c:v>
+                  <c:v>308493</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1077072</c:v>
+                  <c:v>269589</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>955240</c:v>
+                  <c:v>238407</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>838056</c:v>
+                  <c:v>209127</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>723580</c:v>
+                  <c:v>181801</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>627644</c:v>
+                  <c:v>155989</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>535808</c:v>
+                  <c:v>133113</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>467024</c:v>
+                  <c:v>116129</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>392632</c:v>
+                  <c:v>97631</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>314192</c:v>
+                  <c:v>78769</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>212084</c:v>
+                  <c:v>53061</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-5351-4321-B076-84822CFEAA03}"/>
+              <c16:uniqueId val="{00000003-476B-4273-BE60-4157EA253EEB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2432,49 +2505,49 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>data!$F$31:$F$41</c:f>
+              <c:f>data!$D$31:$D$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>847005984</c:v>
+                  <c:v>178242</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>806381136</c:v>
+                  <c:v>169693</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>764634816</c:v>
+                  <c:v>160908</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>741896496</c:v>
+                  <c:v>156123</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>678704400</c:v>
+                  <c:v>142825</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>621732672</c:v>
+                  <c:v>130836</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>545120928</c:v>
+                  <c:v>114714</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>475266528</c:v>
+                  <c:v>100014</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>390780720</c:v>
+                  <c:v>82235</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>300250368</c:v>
+                  <c:v>63184</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>178584912</c:v>
+                  <c:v>37581</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-5351-4321-B076-84822CFEAA03}"/>
+              <c16:uniqueId val="{00000004-476B-4273-BE60-4157EA253EEB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2504,49 +2577,49 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>data!$N$31:$N$41</c:f>
+              <c:f>data!$L$31:$L$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>840253392</c:v>
+                  <c:v>174837</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>795589344</c:v>
+                  <c:v>170518</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>773468784</c:v>
+                  <c:v>163043</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>749100528</c:v>
+                  <c:v>155886</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>680096736</c:v>
+                  <c:v>142736</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>622217376</c:v>
+                  <c:v>131077</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>544070736</c:v>
+                  <c:v>114471</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>475394832</c:v>
+                  <c:v>100015</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>391198896</c:v>
+                  <c:v>82327</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>300179088</c:v>
+                  <c:v>63233</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>178675200</c:v>
+                  <c:v>37593</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-5351-4321-B076-84822CFEAA03}"/>
+              <c16:uniqueId val="{00000005-476B-4273-BE60-4157EA253EEB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2558,7 +2631,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="271"/>
+        <c:gapWidth val="115"/>
         <c:axId val="63278767"/>
         <c:axId val="63271567"/>
       </c:barChart>
@@ -2569,6 +2642,20 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -2576,7 +2663,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -2586,22 +2673,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>Maximum tolerant</a:t>
+                  <a:t>Maximum tolerant angular velocity,            (mrad/s)</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> angular velocity (mrad/s)</a:t>
-                </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -2613,8 +2692,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.32485008169934643"/>
-              <c:y val="0.93568652777777761"/>
+              <c:x val="0.20244488132868207"/>
+              <c:y val="0.92379456451958053"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -2630,7 +2709,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -2662,7 +2741,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -2684,9 +2763,7 @@
       <c:valAx>
         <c:axId val="63271567"/>
         <c:scaling>
-          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
-          <c:min val="10000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2711,7 +2788,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -2721,14 +2798,30 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>overhead signaling messages (X10,000)</a:t>
+                  <a:t>Transmission failures (</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>      </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3200">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -2740,8 +2833,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="5.1879084967320259E-3"/>
-              <c:y val="0.19102625000000001"/>
+              <c:x val="0"/>
+              <c:y val="0.14816434838433554"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -2757,7 +2850,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -2788,9 +2881,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2804,7 +2897,7 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:dispUnits>
-          <c:builtInUnit val="tenThousands"/>
+          <c:builtInUnit val="thousands"/>
         </c:dispUnits>
       </c:valAx>
       <c:spPr>
@@ -2823,10 +2916,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.19603604014196879"/>
-          <c:y val="2.0157108560754946E-2"/>
-          <c:w val="0.60792790832044319"/>
-          <c:h val="5.6593202231630592E-2"/>
+          <c:x val="0.13748227724907175"/>
+          <c:y val="1.0072615735787147E-2"/>
+          <c:w val="0.85050762338661323"/>
+          <c:h val="6.2028675369141889E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -2844,7 +2937,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2912,7 +3005,895 @@
   <c:chart>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.15499852941176467"/>
+          <c:y val="0.10166930667248666"/>
+          <c:w val="0.83395351307189525"/>
+          <c:h val="0.73306120725395552"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DDRS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="ltDnDiag">
+              <a:fgClr>
+                <a:schemeClr val="accent2"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="bg1"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>data!$R$3:$R$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0250000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.05</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.075</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.125</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.175</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data!$F$3:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1181126</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>936431</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>814651</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>679739</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>584509</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>499726</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>413362</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>351325</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>271330</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>211774</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>141454</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5351-4321-B076-84822CFEAA03}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DDRSwG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>data!$N$3:$N$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>740310</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>638324</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>571363</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>496811</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>428811</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>373523</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>318544</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>273367</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>215959</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>170475</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>113273</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5351-4321-B076-84822CFEAA03}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data!$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DTDR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="ltDnDiag">
+              <a:fgClr>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="bg1"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>data!$F$17:$F$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2174088</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1739776</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1425916</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1076052</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>969696</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>836772</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>668696</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>587844</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>499748</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>390240</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>259024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5351-4321-B076-84822CFEAA03}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data!$I$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DTDRwG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg2">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>data!$N$17:$N$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1233972</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1078356</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>953628</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>836508</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>727204</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>623956</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>532452</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>464516</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>390524</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>315076</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>212244</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-5351-4321-B076-84822CFEAA03}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data!$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>OPSPF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="ltDnDiag">
+              <a:fgClr>
+                <a:srgbClr val="FF0000"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="bg1"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>data!$F$31:$F$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>847005984</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>806381136</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>764634816</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>741896496</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>678704400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>621732672</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>545120928</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>475266528</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>390780720</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>300250368</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>178584912</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-5351-4321-B076-84822CFEAA03}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data!$I$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>OPSPFwG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>data!$N$31:$N$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>830825424</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>810301536</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>774780336</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>740770272</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>678281472</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>622877904</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>543966192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>475271280</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>391217904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>300483216</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>178641936</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-5351-4321-B076-84822CFEAA03}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="115"/>
+        <c:axId val="63278767"/>
+        <c:axId val="63271567"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="63278767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="b" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Maximum tolerant</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> angular velocity,            (mrad/s)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3200">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.26882066993464054"/>
+              <c:y val="0.93038120111789002"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="b" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="in"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="63271567"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="63271567"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:min val="10000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Overhead signaling messages </a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3200">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="5.1879084967320259E-3"/>
+              <c:y val="0.19102625000000001"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0_);[Red]\(#,##0\)" sourceLinked="0"/>
+        <c:majorTickMark val="in"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="63278767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:dispUnits>
+          <c:builtInUnit val="tenThousands"/>
+        </c:dispUnits>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.15245759803921566"/>
+          <c:y val="2.0157108560754946E-2"/>
+          <c:w val="0.83515833333333322"/>
+          <c:h val="5.6593202231630592E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12155544429654784"/>
+          <c:y val="9.3853462405313046E-2"/>
+          <c:w val="0.84134155594683235"/>
+          <c:h val="0.74669526310167522"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -2925,7 +3906,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DDR</c:v>
+                  <c:v>DDRS</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3002,37 +3983,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>198.63862984742499</c:v>
+                  <c:v>180.835174771863</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>181.658278589719</c:v>
+                  <c:v>157.93921167627599</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>172.492685991087</c:v>
+                  <c:v>148.72970028071899</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>160.85259046850501</c:v>
+                  <c:v>137.36675281461399</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>152.10987336442301</c:v>
+                  <c:v>130.144109900172</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>144.901837066095</c:v>
+                  <c:v>124.10585815238301</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>135.66363859881099</c:v>
+                  <c:v>117.524433010615</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>130.70449506162299</c:v>
+                  <c:v>114.450138863817</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>121.8690773493</c:v>
+                  <c:v>108.407524293059</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>116.06921817550599</c:v>
+                  <c:v>105.03351510068499</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>108.255762519917</c:v>
+                  <c:v>100.26805632492</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3053,7 +4034,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DDRwG</c:v>
+                  <c:v>DDRSwG</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3087,37 +4068,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>127.02092863714699</c:v>
+                  <c:v>121.795859142379</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123.617573505675</c:v>
+                  <c:v>118.364349859293</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>121.25306703478699</c:v>
+                  <c:v>115.192594622461</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>118.60038483360999</c:v>
+                  <c:v>112.222420216739</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>115.25186119999999</c:v>
+                  <c:v>109.50046390867</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>112.95021199999999</c:v>
+                  <c:v>107.128111245732</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>110.1467533</c:v>
+                  <c:v>105.154736812012</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>107.69130869999999</c:v>
+                  <c:v>103.025955445924</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>104.8887695</c:v>
+                  <c:v>99.972802907019499</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>102.76488449999999</c:v>
+                  <c:v>98.061745545247703</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>98.933883719999997</c:v>
+                  <c:v>95.177337849564907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3266,37 +4247,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>124.1564678</c:v>
+                  <c:v>124.255627808645</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>120.93816289999999</c:v>
+                  <c:v>121.15293310172601</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>118.69496220000001</c:v>
+                  <c:v>118.27733381284401</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>115.8331017</c:v>
+                  <c:v>116.001597551179</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>113.0789936</c:v>
+                  <c:v>113.62764114847</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>110.7496269</c:v>
+                  <c:v>110.468489488442</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>108.113395</c:v>
+                  <c:v>107.88735378460299</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>105.5511394</c:v>
+                  <c:v>105.57870012394</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>103.0726478</c:v>
+                  <c:v>103.045579785021</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>100.3880123</c:v>
+                  <c:v>100.427370491231</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>97.00313783</c:v>
+                  <c:v>97.010767996481803</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3437,37 +4418,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>131.53318820304901</c:v>
+                  <c:v>131.10465400224899</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125.819328392579</c:v>
+                  <c:v>125.76822107408999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>121.192992300516</c:v>
+                  <c:v>121.253613482128</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>117.51520846343401</c:v>
+                  <c:v>117.189758028567</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>113.030476533304</c:v>
+                  <c:v>113.24906699008601</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>109.59675563099</c:v>
+                  <c:v>109.85349027168699</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>106.046529629383</c:v>
+                  <c:v>105.911938252865</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>102.792956326295</c:v>
+                  <c:v>102.76701778739501</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>99.199026695299196</c:v>
+                  <c:v>99.352709081476405</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>95.865488785296293</c:v>
+                  <c:v>95.926576476869798</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>91.908538983389207</c:v>
+                  <c:v>92.011849651265507</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3506,7 +4487,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -3516,22 +4497,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>Maximum tolerant</a:t>
+                  <a:t>Maximum tolerant angular velocity,            (mrad/s)</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> angular velocity (mrad/s)</a:t>
-                </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -3543,8 +4516,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.33189101307189539"/>
-              <c:y val="0.9427420833333332"/>
+              <c:x val="0.21829188076955636"/>
+              <c:y val="0.917015376066739"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -3560,7 +4533,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -3592,7 +4565,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
@@ -3641,7 +4614,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -3651,7 +4624,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -3659,14 +4632,14 @@
                   <a:t>End</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="3200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t> to end propagation delay (ms)</a:t>
                 </a:r>
-                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3200">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -3678,8 +4651,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="3.4683823529411757E-3"/>
-              <c:y val="0.24179430555555556"/>
+              <c:x val="3.7023390927894975E-4"/>
+              <c:y val="0.10309194180946016"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -3695,7 +4668,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
@@ -3726,7 +4699,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -3758,9 +4731,9 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.19492998285604765"/>
+          <c:x val="0.12057419839642287"/>
           <c:y val="1.3254242516344215E-2"/>
-          <c:w val="0.60689827170777855"/>
+          <c:w val="0.83926009814410596"/>
           <c:h val="5.6770269104549569E-2"/>
         </c:manualLayout>
       </c:layout>
@@ -3779,7 +4752,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3828,6 +4801,7 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:userShapes r:id="rId3"/>
 </c:chartSpace>
 </file>
 
@@ -3991,6 +4965,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -5501,6 +6515,509 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6016,31 +7533,211 @@
       <xdr:col>21</xdr:col>
       <xdr:colOff>426277</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>162382</xdr:rowOff>
+      <xdr:rowOff>201206</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="차트 1">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4" name="그룹 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF8C8674-5719-478B-B833-7D7D5693CCCA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9E22430-05A6-54A4-A7EC-BCBFB64B038D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks noChangeAspect="1"/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2473777" y="922561"/>
+          <a:ext cx="12240000" cy="7238824"/>
+          <a:chOff x="2473777" y="922561"/>
+          <a:chExt cx="12240000" cy="7238824"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:graphicFrame macro="">
+        <xdr:nvGraphicFramePr>
+          <xdr:cNvPr id="2" name="차트 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF8C8674-5719-478B-B833-7D7D5693CCCA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGraphicFramePr>
+            <a:graphicFrameLocks noChangeAspect="1"/>
+          </xdr:cNvGraphicFramePr>
+        </xdr:nvGraphicFramePr>
+        <xdr:xfrm>
+          <a:off x="2473777" y="922561"/>
+          <a:ext cx="12240000" cy="7200000"/>
+        </xdr:xfrm>
+        <a:graphic>
+          <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+            <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          </a:graphicData>
+        </a:graphic>
+      </xdr:graphicFrame>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="3" name="그림 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B032584-BA88-4D2F-B3F2-FB7056EB5B4F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11293928" y="7565571"/>
+            <a:ext cx="1040880" cy="595814"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>544285</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>163283</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>537856</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>54249</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="5" name="그룹 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB8F64D0-DAA2-41A9-899E-0312079E0F47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2585356" y="775604"/>
+          <a:ext cx="12240000" cy="7238824"/>
+          <a:chOff x="2473777" y="922561"/>
+          <a:chExt cx="12240000" cy="7238824"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:graphicFrame macro="">
+        <xdr:nvGraphicFramePr>
+          <xdr:cNvPr id="6" name="차트 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB301103-DB1E-053F-2094-34BB7DAF861A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGraphicFramePr>
+            <a:graphicFrameLocks noChangeAspect="1"/>
+          </xdr:cNvGraphicFramePr>
+        </xdr:nvGraphicFramePr>
+        <xdr:xfrm>
+          <a:off x="2473777" y="922561"/>
+          <a:ext cx="12240000" cy="7200000"/>
+        </xdr:xfrm>
+        <a:graphic>
+          <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+            <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          </a:graphicData>
+        </a:graphic>
+      </xdr:graphicFrame>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="7" name="그림 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79164B86-6A99-B4F1-A36F-8C2A3A3DE484}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10504714" y="7565571"/>
+            <a:ext cx="1040880" cy="595814"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>675758</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>98926</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="그림 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CB20E74-A18E-2C69-4F5F-51732E3009F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14287500" y="8572500"/>
+          <a:ext cx="12241829" cy="7242676"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -6050,40 +7747,133 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>676274</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>581024</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>31296</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>181349</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>46724</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>312964</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>173993</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="차트 2">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4" name="그룹 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{373FFFA1-6A47-47AB-ACEB-2D8C341CABE0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8151AC20-CDC8-CAF4-1AEE-1E963A0930FE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks noChangeAspect="1"/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="581024" y="439510"/>
+          <a:ext cx="12372976" cy="7082340"/>
+          <a:chOff x="581024" y="439510"/>
+          <a:chExt cx="12372976" cy="7082340"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:graphicFrame macro="">
+        <xdr:nvGraphicFramePr>
+          <xdr:cNvPr id="3" name="차트 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{373FFFA1-6A47-47AB-ACEB-2D8C341CABE0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGraphicFramePr>
+            <a:graphicFrameLocks noChangeAspect="1"/>
+          </xdr:cNvGraphicFramePr>
+        </xdr:nvGraphicFramePr>
+        <xdr:xfrm>
+          <a:off x="581024" y="439510"/>
+          <a:ext cx="12372976" cy="7009500"/>
+        </xdr:xfrm>
+        <a:graphic>
+          <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+            <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          </a:graphicData>
+        </a:graphic>
+      </xdr:graphicFrame>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="2" name="그림 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{802C4BBC-58C4-4DB0-9FE4-1F6FFF15E371}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8572501" y="6926036"/>
+            <a:ext cx="1040880" cy="595814"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>129524</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>144523</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{037E7A88-D173-7BFB-8C9F-A17C628F2566}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14682107" y="6327321"/>
+          <a:ext cx="12375953" cy="7084166"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -6096,37 +7886,218 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>485774</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:rowOff>171448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>421715</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>132449</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>24160</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="차트 1">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4" name="그룹 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38AB5515-E2B0-440A-B5DB-B40BCB3C5940}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC5D8289-EA86-2469-A2D3-E350FBAE572C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2536450" y="171448"/>
+          <a:ext cx="12240000" cy="7730447"/>
+          <a:chOff x="2536450" y="171448"/>
+          <a:chExt cx="12240000" cy="7730447"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:graphicFrame macro="">
+        <xdr:nvGraphicFramePr>
+          <xdr:cNvPr id="2" name="차트 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38AB5515-E2B0-440A-B5DB-B40BCB3C5940}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGraphicFramePr>
+            <a:graphicFrameLocks/>
+          </xdr:cNvGraphicFramePr>
+        </xdr:nvGraphicFramePr>
+        <xdr:xfrm>
+          <a:off x="2536450" y="171448"/>
+          <a:ext cx="12240000" cy="7672669"/>
+        </xdr:xfrm>
+        <a:graphic>
+          <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+            <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          </a:graphicData>
+        </a:graphic>
+      </xdr:graphicFrame>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="3" name="그림 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D89FDB34-C85C-6D4B-D7E3-FEA370F9546B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11317943" y="7306081"/>
+            <a:ext cx="1040880" cy="595814"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>621329</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>65575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D48E34AA-AD76-D4BA-EB4F-724FB33A3297}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7519147" y="10219765"/>
+          <a:ext cx="12241829" cy="7730398"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>533402</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>6569</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>207164</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>176560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="그림 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D377DDFA-941C-1E86-D91A-B307AEC0EC06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11470343" y="7458481"/>
+          <a:ext cx="1040880" cy="595814"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>336177</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>273948</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>87987</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="그림 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29211C0F-26F4-2EE7-7D4D-DB1FE0C2C387}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1703295" y="10242177"/>
+          <a:ext cx="12241829" cy="7730398"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -6172,7 +8143,95 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>682294</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>59011</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A136593-3C74-ECDE-1AB4-ADD6C60A0D0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15038294" y="7451912"/>
+          <a:ext cx="12302794" cy="7510923"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.66841</cdr:x>
+      <cdr:y>0.91617</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.75305</cdr:x>
+      <cdr:y>0.99552</cdr:y>
+    </cdr:to>
+    <cdr:pic>
+      <cdr:nvPicPr>
+        <cdr:cNvPr id="2" name="그림 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D377DDFA-941C-1E86-D91A-B307AEC0EC06}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </cdr:cNvPicPr>
+      </cdr:nvPicPr>
+      <cdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </cdr:blipFill>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="8219888" y="6878731"/>
+          <a:ext cx="1040880" cy="595814"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+    </cdr:pic>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6492,71 +8551,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B057519C-BCF1-431B-8A6B-7DEB49978D6C}">
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:Y54"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="15.375" customWidth="1"/>
+    <col min="14" max="14" width="34.75" customWidth="1"/>
+    <col min="17" max="17" width="1.75" customWidth="1"/>
+    <col min="18" max="18" width="17.75" customWidth="1"/>
+    <col min="19" max="19" width="9.5" customWidth="1"/>
+    <col min="20" max="20" width="9.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="S1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
       <c r="I2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
         <v>3</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>6</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>7</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>8</v>
       </c>
-      <c r="O2" t="s">
-        <v>9</v>
-      </c>
       <c r="R2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S2" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="S2">
+        <v>24.538650674662598</v>
+      </c>
+      <c r="T2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
@@ -6564,43 +8634,43 @@
         <v>1E-3</v>
       </c>
       <c r="B3">
-        <v>40.587996001999002</v>
+        <v>37.896801599200401</v>
       </c>
       <c r="C3">
-        <v>198.63862984742499</v>
+        <v>180.835174771863</v>
       </c>
       <c r="D3">
-        <v>917241</v>
+        <v>929782</v>
       </c>
       <c r="E3">
-        <v>9.16782608695652</v>
+        <v>9.2931734132933492</v>
       </c>
       <c r="F3">
-        <v>1170690</v>
+        <v>1181126</v>
       </c>
       <c r="G3">
-        <v>11.7010494752623</v>
+        <v>11.805357321339301</v>
       </c>
       <c r="I3">
         <v>1E-3</v>
       </c>
       <c r="J3">
-        <v>25.722418790604699</v>
+        <v>25.1891954022988</v>
       </c>
       <c r="K3">
-        <v>127.02092863714699</v>
+        <v>121.795859142379</v>
       </c>
       <c r="L3">
-        <v>524948</v>
+        <v>592755</v>
       </c>
       <c r="M3">
-        <v>5.2468565717141402</v>
+        <v>5.9245877061469203</v>
       </c>
       <c r="N3">
-        <v>668852</v>
+        <v>740310</v>
       </c>
       <c r="O3">
-        <v>6.6851774112943501</v>
+        <v>7.3994002998500701</v>
       </c>
       <c r="R3">
         <f>A3*1000</f>
@@ -6612,43 +8682,43 @@
         <v>1.0250000000000001E-3</v>
       </c>
       <c r="B4">
-        <v>38.051264367816003</v>
+        <v>34.436701649175397</v>
       </c>
       <c r="C4">
-        <v>181.658278589719</v>
+        <v>157.93921167627599</v>
       </c>
       <c r="D4">
-        <v>717981</v>
+        <v>725393</v>
       </c>
       <c r="E4">
-        <v>7.1762218890554701</v>
+        <v>7.25030484757621</v>
       </c>
       <c r="F4">
-        <v>930785</v>
+        <v>936431</v>
       </c>
       <c r="G4">
-        <v>9.3031984007995998</v>
+        <v>9.3596301849075392</v>
       </c>
       <c r="I4">
         <v>1.0250000000000001E-3</v>
       </c>
       <c r="J4">
-        <v>25.5968815592203</v>
+        <v>25.166896551724101</v>
       </c>
       <c r="K4">
-        <v>123.617573505675</v>
+        <v>118.364349859293</v>
       </c>
       <c r="L4">
-        <v>463036</v>
+        <v>514729</v>
       </c>
       <c r="M4">
-        <v>4.6280459770114897</v>
+        <v>5.14471764117941</v>
       </c>
       <c r="N4">
-        <v>584883</v>
+        <v>638324</v>
       </c>
       <c r="O4">
-        <v>5.8459070464767597</v>
+        <v>6.3800499750124899</v>
       </c>
       <c r="R4">
         <f t="shared" ref="R4:R13" si="0">A4*1000</f>
@@ -6660,43 +8730,43 @@
         <v>1.0499999999999999E-3</v>
       </c>
       <c r="B5">
-        <v>36.727826086956497</v>
+        <v>33.088405797101402</v>
       </c>
       <c r="C5">
-        <v>172.492685991087</v>
+        <v>148.72970028071899</v>
       </c>
       <c r="D5">
-        <v>635083</v>
+        <v>643036</v>
       </c>
       <c r="E5">
-        <v>6.3476561719140401</v>
+        <v>6.4271464267866003</v>
       </c>
       <c r="F5">
-        <v>810992</v>
+        <v>814651</v>
       </c>
       <c r="G5">
-        <v>8.1058670664667591</v>
+        <v>8.1424387806096892</v>
       </c>
       <c r="I5">
         <v>1.0499999999999999E-3</v>
       </c>
       <c r="J5">
-        <v>25.562288855572199</v>
+        <v>24.956991504247799</v>
       </c>
       <c r="K5">
-        <v>121.25306703478699</v>
+        <v>115.192594622461</v>
       </c>
       <c r="L5">
-        <v>421567</v>
+        <v>463209</v>
       </c>
       <c r="M5">
-        <v>4.2135632183908003</v>
+        <v>4.6297751124437703</v>
       </c>
       <c r="N5">
-        <v>525124</v>
+        <v>571363</v>
       </c>
       <c r="O5">
-        <v>5.24861569215392</v>
+        <v>5.7107746126936503</v>
       </c>
       <c r="R5">
         <f t="shared" si="0"/>
@@ -6708,43 +8778,43 @@
         <v>1.075E-3</v>
       </c>
       <c r="B6">
-        <v>34.976691654172903</v>
+        <v>31.4049675162418</v>
       </c>
       <c r="C6">
-        <v>160.85259046850501</v>
+        <v>137.36675281461399</v>
       </c>
       <c r="D6">
-        <v>534017</v>
+        <v>539928</v>
       </c>
       <c r="E6">
-        <v>5.3375012493753102</v>
+        <v>5.39658170914542</v>
       </c>
       <c r="F6">
-        <v>678211</v>
+        <v>679739</v>
       </c>
       <c r="G6">
-        <v>6.7787206396801603</v>
+        <v>6.7939930034982501</v>
       </c>
       <c r="I6">
         <v>1.075E-3</v>
       </c>
       <c r="J6">
-        <v>25.522798600699598</v>
+        <v>24.873533233383299</v>
       </c>
       <c r="K6">
-        <v>118.60038483360999</v>
+        <v>112.222420216739</v>
       </c>
       <c r="L6">
-        <v>381768</v>
+        <v>408459</v>
       </c>
       <c r="M6">
-        <v>3.8157721139430198</v>
+        <v>4.0825487256371797</v>
       </c>
       <c r="N6">
-        <v>469286</v>
+        <v>496811</v>
       </c>
       <c r="O6">
-        <v>4.6905147426286797</v>
+        <v>4.96562718640679</v>
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
@@ -6756,43 +8826,43 @@
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="B7">
-        <v>33.701579210394797</v>
+        <v>30.366866566716599</v>
       </c>
       <c r="C7">
-        <v>152.10987336442301</v>
+        <v>130.144109900172</v>
       </c>
       <c r="D7">
-        <v>465232</v>
+        <v>473486</v>
       </c>
       <c r="E7">
-        <v>4.6499950024987502</v>
+        <v>4.7324937531234301</v>
       </c>
       <c r="F7">
-        <v>580811</v>
+        <v>584509</v>
       </c>
       <c r="G7">
-        <v>5.8052073963018396</v>
+        <v>5.8421689155422198</v>
       </c>
       <c r="I7">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="J7">
-        <v>25.33201399</v>
+        <v>24.782328835582199</v>
       </c>
       <c r="K7">
-        <v>115.25186119999999</v>
+        <v>109.50046390867</v>
       </c>
       <c r="L7">
-        <v>332229</v>
+        <v>357995</v>
       </c>
       <c r="M7">
-        <v>3.3206296850000001</v>
+        <v>3.57816091954022</v>
       </c>
       <c r="N7">
-        <v>403594</v>
+        <v>428811</v>
       </c>
       <c r="O7">
-        <v>4.0339230380000002</v>
+        <v>4.2859670164917496</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
@@ -6804,43 +8874,43 @@
         <v>1.1249999999999999E-3</v>
       </c>
       <c r="B8">
-        <v>32.669155422288803</v>
+        <v>29.469855072463702</v>
       </c>
       <c r="C8">
-        <v>144.901837066095</v>
+        <v>124.10585815238301</v>
       </c>
       <c r="D8">
-        <v>409712</v>
+        <v>414226</v>
       </c>
       <c r="E8">
-        <v>4.0950724637681102</v>
+        <v>4.1401899050474702</v>
       </c>
       <c r="F8">
-        <v>500536</v>
+        <v>499726</v>
       </c>
       <c r="G8">
-        <v>5.0028585707146398</v>
+        <v>4.9947626186906504</v>
       </c>
       <c r="I8">
         <v>1.1249999999999999E-3</v>
       </c>
       <c r="J8">
-        <v>25.27149425</v>
+        <v>24.7260369815092</v>
       </c>
       <c r="K8">
-        <v>112.95021199999999</v>
+        <v>107.128111245732</v>
       </c>
       <c r="L8">
-        <v>291691</v>
+        <v>315944</v>
       </c>
       <c r="M8">
-        <v>2.9154522740000002</v>
+        <v>3.1578610694652598</v>
       </c>
       <c r="N8">
-        <v>351002</v>
+        <v>373523</v>
       </c>
       <c r="O8">
-        <v>3.508265867</v>
+        <v>3.7333633183408201</v>
       </c>
       <c r="R8">
         <f t="shared" si="0"/>
@@ -6852,43 +8922,43 @@
         <v>1.15E-3</v>
       </c>
       <c r="B9">
-        <v>31.303688155922</v>
+        <v>28.5351124437781</v>
       </c>
       <c r="C9">
-        <v>135.66363859881099</v>
+        <v>117.524433010615</v>
       </c>
       <c r="D9">
-        <v>343007</v>
+        <v>348859</v>
       </c>
       <c r="E9">
-        <v>3.4283558220889501</v>
+        <v>3.4868465767116401</v>
       </c>
       <c r="F9">
-        <v>410915</v>
+        <v>413362</v>
       </c>
       <c r="G9">
-        <v>4.10709645177411</v>
+        <v>4.1315542228885498</v>
       </c>
       <c r="I9">
         <v>1.15E-3</v>
       </c>
       <c r="J9">
-        <v>25.243178409999999</v>
+        <v>24.879460269865</v>
       </c>
       <c r="K9">
-        <v>110.1467533</v>
+        <v>105.154736812012</v>
       </c>
       <c r="L9">
-        <v>251203</v>
+        <v>275647</v>
       </c>
       <c r="M9">
-        <v>2.5107746130000002</v>
+        <v>2.7550924537731101</v>
       </c>
       <c r="N9">
-        <v>298051</v>
+        <v>318544</v>
       </c>
       <c r="O9">
-        <v>2.9790204899999999</v>
+        <v>3.1838480759620098</v>
       </c>
       <c r="R9">
         <f t="shared" si="0"/>
@@ -6900,43 +8970,43 @@
         <v>1.175E-3</v>
       </c>
       <c r="B10">
-        <v>30.600439780109902</v>
+        <v>28.129435282358799</v>
       </c>
       <c r="C10">
-        <v>130.70449506162299</v>
+        <v>114.450138863817</v>
       </c>
       <c r="D10">
-        <v>304307</v>
+        <v>309005</v>
       </c>
       <c r="E10">
-        <v>3.0415492253873002</v>
+        <v>3.0885057471264301</v>
       </c>
       <c r="F10">
-        <v>352760</v>
+        <v>351325</v>
       </c>
       <c r="G10">
-        <v>3.5258370814592701</v>
+        <v>3.5114942528735602</v>
       </c>
       <c r="I10">
         <v>1.175E-3</v>
       </c>
       <c r="J10">
-        <v>25.07311344</v>
+        <v>24.7492253873063</v>
       </c>
       <c r="K10">
-        <v>107.69130869999999</v>
+        <v>103.025955445924</v>
       </c>
       <c r="L10">
-        <v>217952</v>
+        <v>242059</v>
       </c>
       <c r="M10">
-        <v>2.1784307850000002</v>
+        <v>2.4193803098450699</v>
       </c>
       <c r="N10">
-        <v>254605</v>
+        <v>273367</v>
       </c>
       <c r="O10">
-        <v>2.5447776110000002</v>
+        <v>2.7323038480759601</v>
       </c>
       <c r="R10">
         <f t="shared" si="0"/>
@@ -6948,43 +9018,43 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="B11">
-        <v>29.281439280359798</v>
+        <v>27.2581909045477</v>
       </c>
       <c r="C11">
-        <v>121.8690773493</v>
+        <v>108.407524293059</v>
       </c>
       <c r="D11">
-        <v>240404</v>
+        <v>246242</v>
       </c>
       <c r="E11">
-        <v>2.40283858070964</v>
+        <v>2.46118940529735</v>
       </c>
       <c r="F11">
-        <v>270591</v>
+        <v>271330</v>
       </c>
       <c r="G11">
-        <v>2.7045577211394298</v>
+        <v>2.7119440279860001</v>
       </c>
       <c r="I11">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="J11">
-        <v>25.00367816</v>
+        <v>24.599170414792599</v>
       </c>
       <c r="K11">
-        <v>104.8887695</v>
+        <v>99.972802907019499</v>
       </c>
       <c r="L11">
-        <v>177395</v>
+        <v>197375</v>
       </c>
       <c r="M11">
-        <v>1.7730634679999999</v>
+        <v>1.9727636181909001</v>
       </c>
       <c r="N11">
-        <v>201707</v>
+        <v>215959</v>
       </c>
       <c r="O11">
-        <v>2.0160619689999999</v>
+        <v>2.1585107446276801</v>
       </c>
       <c r="R11">
         <f t="shared" si="0"/>
@@ -6996,43 +9066,43 @@
         <v>1.225E-3</v>
       </c>
       <c r="B12">
-        <v>28.428275862068901</v>
+        <v>26.7699050474762</v>
       </c>
       <c r="C12">
-        <v>116.06921817550599</v>
+        <v>105.03351510068499</v>
       </c>
       <c r="D12">
-        <v>198375</v>
+        <v>203959</v>
       </c>
       <c r="E12">
-        <v>1.9827586206896499</v>
+        <v>2.0385707146426699</v>
       </c>
       <c r="F12">
-        <v>211128</v>
+        <v>211774</v>
       </c>
       <c r="G12">
-        <v>2.1102248875562202</v>
+        <v>2.1166816591704101</v>
       </c>
       <c r="I12">
         <v>1.225E-3</v>
       </c>
       <c r="J12">
-        <v>25.035572210000002</v>
+        <v>24.5712943528235</v>
       </c>
       <c r="K12">
-        <v>102.76488449999999</v>
+        <v>98.061745545247703</v>
       </c>
       <c r="L12">
-        <v>148896</v>
+        <v>163748</v>
       </c>
       <c r="M12">
-        <v>1.4882158919999999</v>
+        <v>1.6366616691654099</v>
       </c>
       <c r="N12">
-        <v>160662</v>
+        <v>170475</v>
       </c>
       <c r="O12">
-        <v>1.605817091</v>
+        <v>1.7038980509745101</v>
       </c>
       <c r="R12">
         <f t="shared" si="0"/>
@@ -7044,43 +9114,43 @@
         <v>1.25E-3</v>
       </c>
       <c r="B13">
-        <v>27.307146426786598</v>
+        <v>26.121439280359802</v>
       </c>
       <c r="C13">
-        <v>108.255762519917</v>
+        <v>100.26805632492</v>
       </c>
       <c r="D13">
-        <v>140874</v>
+        <v>145987</v>
       </c>
       <c r="E13">
-        <v>1.4080359820089901</v>
+        <v>1.4591404297851001</v>
       </c>
       <c r="F13">
-        <v>137533</v>
+        <v>141454</v>
       </c>
       <c r="G13">
-        <v>1.37464267866066</v>
+        <v>1.41383308345827</v>
       </c>
       <c r="I13">
         <v>1.25E-3</v>
       </c>
       <c r="J13">
-        <v>24.819900050000001</v>
+        <v>24.4689255372313</v>
       </c>
       <c r="K13">
-        <v>98.933883719999997</v>
+        <v>95.177337849564907</v>
       </c>
       <c r="L13">
-        <v>106651</v>
+        <v>116642</v>
       </c>
       <c r="M13">
-        <v>1.065977011</v>
+        <v>1.16583708145927</v>
       </c>
       <c r="N13">
-        <v>105043</v>
+        <v>113273</v>
       </c>
       <c r="O13">
-        <v>1.049905047</v>
+        <v>1.1321639180409699</v>
       </c>
       <c r="R13">
         <f t="shared" si="0"/>
@@ -7092,51 +9162,59 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="R15">
+        <f>F3/F17</f>
+        <v>0.54327423728938296</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
         <v>3</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>4</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>5</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>6</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>7</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>8</v>
       </c>
-      <c r="G16" t="s">
-        <v>9</v>
-      </c>
       <c r="I16" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" t="s">
         <v>3</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>4</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>5</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>6</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>7</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>8</v>
       </c>
-      <c r="O16" t="s">
-        <v>9</v>
+      <c r="R16">
+        <f t="shared" ref="R16:R21" si="1">F4/F18</f>
+        <v>0.5382480273322543</v>
       </c>
       <c r="S16">
         <v>1E-3</v>
@@ -7186,22 +9264,26 @@
         <v>1E-3</v>
       </c>
       <c r="J17">
-        <v>25.157141429999999</v>
+        <v>25.192163918040901</v>
       </c>
       <c r="K17">
-        <v>124.1564678</v>
+        <v>124.255627808645</v>
       </c>
       <c r="L17">
-        <v>308119</v>
+        <v>308493</v>
       </c>
       <c r="M17">
-        <v>3.0796501749999998</v>
+        <v>3.0833883058470701</v>
       </c>
       <c r="N17">
-        <v>1232476</v>
+        <v>1233972</v>
       </c>
       <c r="O17">
-        <v>12.318600699999999</v>
+        <v>12.3335532233883</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="1"/>
+        <v>0.57131766527621541</v>
       </c>
       <c r="S17">
         <v>1.0250000000000001E-3</v>
@@ -7251,22 +9333,26 @@
         <v>1.0250000000000001E-3</v>
       </c>
       <c r="J18">
-        <v>25.075702150000001</v>
+        <v>25.1360219890054</v>
       </c>
       <c r="K18">
-        <v>120.93816289999999</v>
+        <v>121.15293310172601</v>
       </c>
       <c r="L18">
-        <v>269268</v>
+        <v>269589</v>
       </c>
       <c r="M18">
-        <v>2.6913343329999999</v>
+        <v>2.69454272863568</v>
       </c>
       <c r="N18">
-        <v>1077072</v>
+        <v>1078356</v>
       </c>
       <c r="O18">
-        <v>10.765337329999999</v>
+        <v>10.7781709145427</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="1"/>
+        <v>0.63169716705140644</v>
       </c>
       <c r="S18">
         <v>1.0499999999999999E-3</v>
@@ -7316,22 +9402,26 @@
         <v>1.0499999999999999E-3</v>
       </c>
       <c r="J19">
-        <v>25.144677659999999</v>
+        <v>25.073783108445699</v>
       </c>
       <c r="K19">
-        <v>118.69496220000001</v>
+        <v>118.27733381284401</v>
       </c>
       <c r="L19">
-        <v>238810</v>
+        <v>238407</v>
       </c>
       <c r="M19">
-        <v>2.3869065470000002</v>
+        <v>2.3828785607196399</v>
       </c>
       <c r="N19">
-        <v>955240</v>
+        <v>953628</v>
       </c>
       <c r="O19">
-        <v>9.5476261870000005</v>
+        <v>9.5315142428785595</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="1"/>
+        <v>0.60277550902550903</v>
       </c>
       <c r="S19">
         <v>1.075E-3</v>
@@ -7381,22 +9471,26 @@
         <v>1.075E-3</v>
       </c>
       <c r="J20">
-        <v>25.11894053</v>
+        <v>25.151664167916</v>
       </c>
       <c r="K20">
-        <v>115.8331017</v>
+        <v>116.001597551179</v>
       </c>
       <c r="L20">
-        <v>209514</v>
+        <v>209127</v>
       </c>
       <c r="M20">
-        <v>2.0940929540000002</v>
+        <v>2.0902248875562202</v>
       </c>
       <c r="N20">
-        <v>838056</v>
+        <v>836508</v>
       </c>
       <c r="O20">
-        <v>8.3763718140000005</v>
+        <v>8.3608995502248806</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="1"/>
+        <v>0.59720688550764123</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
@@ -7425,22 +9519,26 @@
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="J21">
-        <v>24.962268869999999</v>
+        <v>25.081489255372301</v>
       </c>
       <c r="K21">
-        <v>113.0789936</v>
+        <v>113.62764114847</v>
       </c>
       <c r="L21">
-        <v>180895</v>
+        <v>181801</v>
       </c>
       <c r="M21">
-        <v>1.8080459769999999</v>
+        <v>1.8171014492753601</v>
       </c>
       <c r="N21">
-        <v>723580</v>
+        <v>727204</v>
       </c>
       <c r="O21">
-        <v>7.2321839079999997</v>
+        <v>7.2684057971014404</v>
+      </c>
+      <c r="R21">
+        <f>F9/F23</f>
+        <v>0.61816131695120058</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
@@ -7469,22 +9567,29 @@
         <v>1.1249999999999999E-3</v>
       </c>
       <c r="J22">
-        <v>24.92835582</v>
+        <v>24.8646176911544</v>
       </c>
       <c r="K22">
-        <v>110.7496269</v>
+        <v>110.468489488442</v>
       </c>
       <c r="L22">
-        <v>156911</v>
+        <v>155989</v>
       </c>
       <c r="M22">
-        <v>1.5683258369999999</v>
+        <v>1.5591104447776101</v>
       </c>
       <c r="N22">
-        <v>627644</v>
+        <v>623956</v>
       </c>
       <c r="O22">
-        <v>6.2733033479999998</v>
+        <v>6.2364417791104403</v>
+      </c>
+      <c r="R22">
+        <f t="shared" ref="R22:R25" si="2">F10/F24</f>
+        <v>0.59765005681779515</v>
+      </c>
+      <c r="S22" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
@@ -7513,22 +9618,35 @@
         <v>1.15E-3</v>
       </c>
       <c r="J23">
-        <v>24.952043979999999</v>
+        <v>24.925097451274301</v>
       </c>
       <c r="K23">
-        <v>108.113395</v>
+        <v>107.88735378460299</v>
       </c>
       <c r="L23">
-        <v>133952</v>
+        <v>133113</v>
       </c>
       <c r="M23">
-        <v>1.3388505749999999</v>
+        <v>1.33046476761619</v>
       </c>
       <c r="N23">
-        <v>535808</v>
+        <v>532452</v>
       </c>
       <c r="O23">
-        <v>5.3554022989999996</v>
+        <v>5.3218590704647601</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="2"/>
+        <v>0.54293363855383114</v>
+      </c>
+      <c r="S23" t="s">
+        <v>15</v>
+      </c>
+      <c r="T23" t="s">
+        <v>16</v>
+      </c>
+      <c r="U23" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
@@ -7557,22 +9675,38 @@
         <v>1.175E-3</v>
       </c>
       <c r="J24">
-        <v>24.807995999999999</v>
+        <v>24.786266866566699</v>
       </c>
       <c r="K24">
-        <v>105.5511394</v>
+        <v>105.57870012394</v>
       </c>
       <c r="L24">
-        <v>116756</v>
+        <v>116129</v>
       </c>
       <c r="M24">
-        <v>1.166976512</v>
+        <v>1.1607096451774099</v>
       </c>
       <c r="N24">
-        <v>467024</v>
+        <v>464516</v>
       </c>
       <c r="O24">
-        <v>4.6679060469999998</v>
+        <v>4.6428385807096397</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="2"/>
+        <v>0.54267630176301762</v>
+      </c>
+      <c r="S24">
+        <f>(D3-L3)/D3 * 100</f>
+        <v>36.247959199038057</v>
+      </c>
+      <c r="T24">
+        <f>(F3-N3)/F3 * 100</f>
+        <v>37.321674402222968</v>
+      </c>
+      <c r="U24">
+        <f>C3-K3</f>
+        <v>59.039315629483994</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
@@ -7601,22 +9735,38 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="J25">
-        <v>24.68882559</v>
+        <v>24.679520239879999</v>
       </c>
       <c r="K25">
-        <v>103.0726478</v>
+        <v>103.045579785021</v>
       </c>
       <c r="L25">
-        <v>98158</v>
+        <v>97631</v>
       </c>
       <c r="M25">
-        <v>0.981089455</v>
+        <v>0.97582208895552203</v>
       </c>
       <c r="N25">
-        <v>392632</v>
+        <v>390524</v>
       </c>
       <c r="O25">
-        <v>3.9243578210000001</v>
+        <v>3.9032883558220801</v>
+      </c>
+      <c r="R25">
+        <f>F13/F27</f>
+        <v>0.54610383593798262</v>
+      </c>
+      <c r="S25">
+        <f>(D17-L17)/D17 * 100</f>
+        <v>43.241855895437538</v>
+      </c>
+      <c r="T25">
+        <f>(F17-N17)/F17 * 100</f>
+        <v>43.241855895437538</v>
+      </c>
+      <c r="U25">
+        <f>C17-K17</f>
+        <v>81.167949421838998</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
@@ -7645,22 +9795,37 @@
         <v>1.225E-3</v>
       </c>
       <c r="J26">
-        <v>24.60172914</v>
+        <v>24.599330334832501</v>
       </c>
       <c r="K26">
-        <v>100.3880123</v>
+        <v>100.427370491231</v>
       </c>
       <c r="L26">
-        <v>78548</v>
+        <v>78769</v>
       </c>
       <c r="M26">
-        <v>0.78508745599999996</v>
+        <v>0.78729635182408797</v>
       </c>
       <c r="N26">
-        <v>314192</v>
+        <v>315076</v>
       </c>
       <c r="O26">
-        <v>3.1403498249999999</v>
+        <v>3.1491854072963501</v>
+      </c>
+      <c r="R26" t="s">
+        <v>19</v>
+      </c>
+      <c r="S26">
+        <f>(S24+S25)/2</f>
+        <v>39.744907547237801</v>
+      </c>
+      <c r="T26">
+        <f>(T24+T25)/2</f>
+        <v>40.281765148830253</v>
+      </c>
+      <c r="U26">
+        <f>(U24+U25)/2</f>
+        <v>70.103632525661496</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
@@ -7689,74 +9854,85 @@
         <v>1.25E-3</v>
       </c>
       <c r="J27">
-        <v>24.515902050000001</v>
+        <v>24.504397801099401</v>
       </c>
       <c r="K27">
-        <v>97.00313783</v>
+        <v>97.010767996481803</v>
       </c>
       <c r="L27">
-        <v>53021</v>
+        <v>53061</v>
       </c>
       <c r="M27">
-        <v>0.52994502700000001</v>
+        <v>0.53034482758620605</v>
       </c>
       <c r="N27">
-        <v>212084</v>
+        <v>212244</v>
       </c>
       <c r="O27">
-        <v>2.1197801100000002</v>
+        <v>2.1213793103448202</v>
+      </c>
+      <c r="R27" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="S29">
+        <f>C3-K3</f>
+        <v>59.039315629483994</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
         <v>3</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>4</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>5</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>6</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>7</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>8</v>
       </c>
-      <c r="G30" t="s">
-        <v>9</v>
-      </c>
       <c r="I30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J30" t="s">
         <v>3</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>4</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>5</v>
       </c>
-      <c r="L30" t="s">
+      <c r="M30" t="s">
         <v>6</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>7</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>8</v>
       </c>
-      <c r="O30" t="s">
-        <v>9</v>
+      <c r="S30">
+        <f>C17-K17</f>
+        <v>81.167949421838998</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
@@ -7787,22 +9963,22 @@
         <v>1E-3</v>
       </c>
       <c r="J31">
-        <v>30.437239249037201</v>
+        <v>30.334299526598699</v>
       </c>
       <c r="K31">
-        <v>131.53318820304901</v>
+        <v>131.10465400224899</v>
       </c>
       <c r="L31">
-        <v>176821</v>
+        <v>174837</v>
       </c>
       <c r="M31">
-        <v>1.77331715340179</v>
+        <v>1.7535605391960201</v>
       </c>
       <c r="N31">
-        <v>840253392</v>
+        <v>830825424</v>
       </c>
       <c r="O31">
-        <v>8426.8031129653391</v>
+        <v>8332.9196822594804</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
@@ -7833,22 +10009,22 @@
         <v>1.0250000000000001E-3</v>
       </c>
       <c r="J32">
-        <v>29.647644718779102</v>
+        <v>29.605405513704099</v>
       </c>
       <c r="K32">
-        <v>125.819328392579</v>
+        <v>125.76822107408999</v>
       </c>
       <c r="L32">
-        <v>167422</v>
+        <v>170518</v>
       </c>
       <c r="M32">
-        <v>1.6776255799272499</v>
+        <v>1.7081864080782101</v>
       </c>
       <c r="N32">
-        <v>795589344</v>
+        <v>810301536</v>
       </c>
       <c r="O32">
-        <v>7972.0767558142998</v>
+        <v>8117.30181118769</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
@@ -7879,22 +10055,22 @@
         <v>1.0499999999999999E-3</v>
       </c>
       <c r="J33">
-        <v>28.989098444351001</v>
+        <v>28.9913512647774</v>
       </c>
       <c r="K33">
-        <v>121.192992300516</v>
+        <v>121.253613482128</v>
       </c>
       <c r="L33">
-        <v>162767</v>
+        <v>163043</v>
       </c>
       <c r="M33">
-        <v>1.6293971609906499</v>
+        <v>1.63207839918317</v>
       </c>
       <c r="N33">
-        <v>773468784</v>
+        <v>774780336</v>
       </c>
       <c r="O33">
-        <v>7742.89530902756</v>
+        <v>7755.6365529184404</v>
       </c>
       <c r="Q33">
         <v>1.075E-3</v>
@@ -7946,22 +10122,22 @@
         <v>1.075E-3</v>
       </c>
       <c r="J34">
-        <v>28.490885091149</v>
+        <v>28.4227518678175</v>
       </c>
       <c r="K34">
-        <v>117.51520846343401</v>
+        <v>117.189758028567</v>
       </c>
       <c r="L34">
-        <v>157639</v>
+        <v>155886</v>
       </c>
       <c r="M34">
-        <v>1.5763742362576301</v>
+        <v>1.55912505125871</v>
       </c>
       <c r="N34">
-        <v>749100528</v>
+        <v>740770272</v>
       </c>
       <c r="O34">
-        <v>7490.9303706962901</v>
+        <v>7408.9622435813999</v>
       </c>
       <c r="Q34">
         <v>1.0499999999999999E-3</v>
@@ -8002,33 +10178,33 @@
         <v>1.4278930267433101</v>
       </c>
       <c r="F35">
-        <f t="shared" ref="F35:F41" si="1">D35*3*1584</f>
+        <f t="shared" ref="F35" si="3">D35*3*1584</f>
         <v>678704400</v>
       </c>
       <c r="G35">
-        <f t="shared" ref="G35" si="2">F35/A35</f>
+        <f t="shared" ref="G35" si="4">F35/A35</f>
         <v>617004000000</v>
       </c>
       <c r="I35">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="J35">
-        <v>27.837273936037199</v>
+        <v>27.908460138769399</v>
       </c>
       <c r="K35">
-        <v>113.030476533304</v>
+        <v>113.24906699008601</v>
       </c>
       <c r="L35">
-        <v>143118</v>
+        <v>142736</v>
       </c>
       <c r="M35">
-        <v>1.43079368570485</v>
+        <v>1.4270460498690201</v>
       </c>
       <c r="N35">
-        <v>680096736</v>
+        <v>678281472</v>
       </c>
       <c r="O35">
-        <v>6799.1315944694898</v>
+        <v>6781.3228289776198</v>
       </c>
       <c r="Q35">
         <v>1.0250000000000001E-3</v>
@@ -8080,22 +10256,22 @@
         <v>1.1249999999999999E-3</v>
       </c>
       <c r="J36">
-        <v>27.388479069209499</v>
+        <v>27.4427351965135</v>
       </c>
       <c r="K36">
-        <v>109.59675563099</v>
+        <v>109.85349027168699</v>
       </c>
       <c r="L36">
-        <v>130938</v>
+        <v>131077</v>
       </c>
       <c r="M36">
-        <v>1.3088041261844701</v>
+        <v>1.31019351485346</v>
       </c>
       <c r="N36">
-        <v>622217376</v>
+        <v>622877904</v>
       </c>
       <c r="O36">
-        <v>6219.43720762864</v>
+        <v>6226.0395825836604</v>
       </c>
       <c r="Q36">
         <v>1E-3</v>
@@ -8136,33 +10312,33 @@
         <v>1.14656671664167</v>
       </c>
       <c r="F37">
-        <f t="shared" ref="F37:F41" si="3">D37*3*1584</f>
+        <f t="shared" ref="F37:F38" si="5">D37*3*1584</f>
         <v>545120928</v>
       </c>
       <c r="G37">
-        <f t="shared" ref="G37:G38" si="4">F37/A37</f>
+        <f t="shared" ref="G37:G38" si="6">F37/A37</f>
         <v>474018198260.86957</v>
       </c>
       <c r="I37">
         <v>1.15E-3</v>
       </c>
       <c r="J37">
-        <v>26.940748440748401</v>
+        <v>26.9018361370156</v>
       </c>
       <c r="K37">
-        <v>106.046529629383</v>
+        <v>105.911938252865</v>
       </c>
       <c r="L37">
-        <v>114493</v>
+        <v>114471</v>
       </c>
       <c r="M37">
-        <v>1.1443806972653101</v>
+        <v>1.1441722390476401</v>
       </c>
       <c r="N37">
-        <v>544070736</v>
+        <v>543966192</v>
       </c>
       <c r="O37">
-        <v>5438.0970734047596</v>
+        <v>5437.1064799544201</v>
       </c>
       <c r="Q37">
         <v>1.1000000000000001E-3</v>
@@ -8203,33 +10379,33 @@
         <v>0.99965017141600598</v>
       </c>
       <c r="F38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>475266528</v>
       </c>
       <c r="G38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>404482151489.36169</v>
       </c>
       <c r="I38">
         <v>1.175E-3</v>
       </c>
       <c r="J38">
-        <v>26.498625673420001</v>
+        <v>26.4699597197373</v>
       </c>
       <c r="K38">
-        <v>102.792956326295</v>
+        <v>102.76701778739501</v>
       </c>
       <c r="L38">
-        <v>100041</v>
+        <v>100015</v>
       </c>
       <c r="M38">
-        <v>0.99992003918080097</v>
+        <v>0.99966016651840595</v>
       </c>
       <c r="N38">
-        <v>475394832</v>
+        <v>475271280</v>
       </c>
       <c r="O38">
-        <v>4751.62002618716</v>
+        <v>4750.3851112954599</v>
       </c>
       <c r="Q38">
         <v>1.1249999999999999E-3</v>
@@ -8281,22 +10457,22 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="J39">
-        <v>25.987686156921502</v>
+        <v>26.025747126436698</v>
       </c>
       <c r="K39">
-        <v>99.199026695299196</v>
+        <v>99.352709081476405</v>
       </c>
       <c r="L39">
-        <v>82323</v>
+        <v>82327</v>
       </c>
       <c r="M39">
-        <v>0.82281859070464702</v>
+        <v>0.82285857071464197</v>
       </c>
       <c r="N39">
-        <v>391198896</v>
+        <v>391217904</v>
       </c>
       <c r="O39">
-        <v>3910.0339430284798</v>
+        <v>3910.22392803598</v>
       </c>
       <c r="Q39">
         <v>1.15E-3</v>
@@ -8348,22 +10524,22 @@
         <v>1.225E-3</v>
       </c>
       <c r="J40">
-        <v>25.563308345827</v>
+        <v>25.590934532733598</v>
       </c>
       <c r="K40">
-        <v>95.865488785296293</v>
+        <v>95.926576476869798</v>
       </c>
       <c r="L40">
-        <v>63169</v>
+        <v>63233</v>
       </c>
       <c r="M40">
-        <v>0.63137431284357803</v>
+        <v>0.63201399300349803</v>
       </c>
       <c r="N40">
-        <v>300179088</v>
+        <v>300483216</v>
       </c>
       <c r="O40">
-        <v>3000.2907346326801</v>
+        <v>3003.3304947526199</v>
       </c>
       <c r="Q40">
         <v>1.175E-3</v>
@@ -8404,33 +10580,33 @@
         <v>0.37562218890554699</v>
       </c>
       <c r="F41">
-        <f t="shared" ref="F41" si="5">D41*3*1584</f>
+        <f t="shared" ref="F41" si="7">D41*3*1584</f>
         <v>178584912</v>
       </c>
       <c r="G41">
-        <f t="shared" ref="G41" si="6">F41/A41</f>
+        <f t="shared" ref="G41" si="8">F41/A41</f>
         <v>142867929600</v>
       </c>
       <c r="I41">
         <v>1.25E-3</v>
       </c>
       <c r="J41">
-        <v>25.0803698150924</v>
+        <v>25.0942628685657</v>
       </c>
       <c r="K41">
-        <v>91.908538983389207</v>
+        <v>92.011849651265507</v>
       </c>
       <c r="L41">
-        <v>37600</v>
+        <v>37593</v>
       </c>
       <c r="M41">
-        <v>0.37581209395302301</v>
+        <v>0.37574212893553199</v>
       </c>
       <c r="N41">
-        <v>178675200</v>
+        <v>178641936</v>
       </c>
       <c r="O41">
-        <v>1785.85907046476</v>
+        <v>1785.5265967016401</v>
       </c>
       <c r="Q41">
         <v>1.25E-3</v>
@@ -8498,6 +10674,117 @@
       </c>
       <c r="W43">
         <v>3910.0339430284798</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="F44">
+        <f>F31/F17</f>
+        <v>389.59139832426285</v>
+      </c>
+      <c r="H44">
+        <f>(C3-K3)/C3</f>
+        <v>0.32648137014254264</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="F45">
+        <f t="shared" ref="F45:F59" si="9">F32/F18</f>
+        <v>463.49710307533843</v>
+      </c>
+      <c r="H45">
+        <f t="shared" ref="H45:H54" si="10">(C4-K4)/C4</f>
+        <v>0.2505702124061413</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="F46">
+        <f t="shared" si="9"/>
+        <v>536.24113622401319</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="10"/>
+        <v>0.22549030620621555</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="F47">
+        <f t="shared" si="9"/>
+        <v>689.46156505447698</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="10"/>
+        <v>0.1830452571868611</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="F48">
+        <f t="shared" si="9"/>
+        <v>699.91461241461241</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="10"/>
+        <v>0.15862143901354323</v>
+      </c>
+    </row>
+    <row r="49" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F49">
+        <f t="shared" si="9"/>
+        <v>743.0132365805739</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="10"/>
+        <v>0.13680052786714492</v>
+      </c>
+    </row>
+    <row r="50" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F50">
+        <f t="shared" si="9"/>
+        <v>815.19992343306978</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="10"/>
+        <v>0.10525212401991119</v>
+      </c>
+      <c r="K50" s="1"/>
+    </row>
+    <row r="51" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F51">
+        <f t="shared" si="9"/>
+        <v>808.49090575050525</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="10"/>
+        <v>9.9817995253693129E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F52">
+        <f t="shared" si="9"/>
+        <v>781.95554559497987</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="10"/>
+        <v>7.780568222587432E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F53">
+        <f t="shared" si="9"/>
+        <v>769.39926199261993</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="10"/>
+        <v>6.6376618441781762E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F54">
+        <f t="shared" si="9"/>
+        <v>689.45314719871521</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="10"/>
+        <v>5.0771089636549326E-2</v>
       </c>
     </row>
   </sheetData>
